--- a/research/traditional_assets/database/data/myanmar/myanmar_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/myanmar/myanmar_real_estate_development.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1246276454083872</v>
+        <v>0.1242594369430803</v>
       </c>
       <c r="C2">
-        <v>387.9000432090697</v>
+        <v>385.996967762824</v>
       </c>
       <c r="D2">
-        <v>288.5000432090697</v>
+        <v>289.853967762824</v>
       </c>
       <c r="E2">
-        <v>-198</v>
+        <v>-194.743</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.257000000000001</v>
       </c>
       <c r="G2">
         <v>99.40000000000001</v>
@@ -1445,28 +1445,28 @@
         <v>59</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1638271</v>
       </c>
       <c r="N2">
-        <v>59</v>
+        <v>58.8361729</v>
       </c>
       <c r="O2">
-        <v>18.88</v>
+        <v>18.827575328</v>
       </c>
       <c r="P2">
-        <v>40.12</v>
+        <v>40.008597572</v>
       </c>
       <c r="Q2">
-        <v>52.32000000000001</v>
+        <v>52.208597572</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1246276454083872</v>
+        <v>0.1251690878212933</v>
       </c>
       <c r="T2">
-        <v>0.4457367247241992</v>
+        <v>0.4487983507122039</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>360.1357772920352</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1242594369430803</v>
+        <v>0.1238912284777735</v>
       </c>
       <c r="C3">
-        <v>385.996967762824</v>
+        <v>384.1066601137251</v>
       </c>
       <c r="D3">
-        <v>289.853967762824</v>
+        <v>291.2206601137251</v>
       </c>
       <c r="E3">
-        <v>-194.743</v>
+        <v>-191.486</v>
       </c>
       <c r="F3">
-        <v>3.257000000000001</v>
+        <v>6.514000000000001</v>
       </c>
       <c r="G3">
         <v>99.40000000000001</v>
@@ -1527,28 +1527,28 @@
         <v>59</v>
       </c>
       <c r="M3">
-        <v>0.1638271</v>
+        <v>0.3276542000000001</v>
       </c>
       <c r="N3">
-        <v>58.8361729</v>
+        <v>58.6723458</v>
       </c>
       <c r="O3">
-        <v>18.827575328</v>
+        <v>18.775150656</v>
       </c>
       <c r="P3">
-        <v>40.008597572</v>
+        <v>39.897195144</v>
       </c>
       <c r="Q3">
-        <v>52.208597572</v>
+        <v>52.097195144</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1251690878212933</v>
+        <v>0.1257215800793607</v>
       </c>
       <c r="T3">
-        <v>0.4487983507122039</v>
+        <v>0.4519224588632289</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>360.1357772920352</v>
+        <v>180.0678886460176</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1238912284777735</v>
+        <v>0.1235230200124666</v>
       </c>
       <c r="C4">
-        <v>384.1066601137251</v>
+        <v>382.2293017219503</v>
       </c>
       <c r="D4">
-        <v>291.2206601137251</v>
+        <v>292.6003017219503</v>
       </c>
       <c r="E4">
-        <v>-191.486</v>
+        <v>-188.229</v>
       </c>
       <c r="F4">
-        <v>6.514000000000001</v>
+        <v>9.771000000000001</v>
       </c>
       <c r="G4">
         <v>99.40000000000001</v>
@@ -1609,28 +1609,28 @@
         <v>59</v>
       </c>
       <c r="M4">
-        <v>0.3276542000000001</v>
+        <v>0.4914813</v>
       </c>
       <c r="N4">
-        <v>58.6723458</v>
+        <v>58.5085187</v>
       </c>
       <c r="O4">
-        <v>18.775150656</v>
+        <v>18.722725984</v>
       </c>
       <c r="P4">
-        <v>39.897195144</v>
+        <v>39.785792716</v>
       </c>
       <c r="Q4">
-        <v>52.097195144</v>
+        <v>51.98579271600001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1257215800793607</v>
+        <v>0.126285463930378</v>
       </c>
       <c r="T4">
-        <v>0.4519224588632289</v>
+        <v>0.4551109816153061</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>180.0678886460176</v>
+        <v>120.0452590973451</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1235230200124666</v>
+        <v>0.1231548115471598</v>
       </c>
       <c r="C5">
-        <v>382.2293017219503</v>
+        <v>380.3650775026745</v>
       </c>
       <c r="D5">
-        <v>292.6003017219503</v>
+        <v>293.9930775026745</v>
       </c>
       <c r="E5">
-        <v>-188.229</v>
+        <v>-184.972</v>
       </c>
       <c r="F5">
-        <v>9.771000000000001</v>
+        <v>13.028</v>
       </c>
       <c r="G5">
         <v>99.40000000000001</v>
@@ -1691,28 +1691,28 @@
         <v>59</v>
       </c>
       <c r="M5">
-        <v>0.4914813</v>
+        <v>0.6553084000000001</v>
       </c>
       <c r="N5">
-        <v>58.5085187</v>
+        <v>58.3446916</v>
       </c>
       <c r="O5">
-        <v>18.722725984</v>
+        <v>18.670301312</v>
       </c>
       <c r="P5">
-        <v>39.785792716</v>
+        <v>39.674390288</v>
       </c>
       <c r="Q5">
-        <v>51.98579271600001</v>
+        <v>51.874390288</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.126285463930378</v>
+        <v>0.1268610953616248</v>
       </c>
       <c r="T5">
-        <v>0.4551109816153061</v>
+        <v>0.4583659319247182</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>120.0452590973451</v>
+        <v>90.03394432300881</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1231548115471598</v>
+        <v>0.1227866030818529</v>
       </c>
       <c r="C6">
-        <v>380.3650775026745</v>
+        <v>378.5141759086919</v>
       </c>
       <c r="D6">
-        <v>293.9930775026745</v>
+        <v>295.399175908692</v>
       </c>
       <c r="E6">
-        <v>-184.972</v>
+        <v>-181.715</v>
       </c>
       <c r="F6">
-        <v>13.028</v>
+        <v>16.285</v>
       </c>
       <c r="G6">
         <v>99.40000000000001</v>
@@ -1773,28 +1773,28 @@
         <v>59</v>
       </c>
       <c r="M6">
-        <v>0.6553084000000001</v>
+        <v>0.8191355000000001</v>
       </c>
       <c r="N6">
-        <v>58.3446916</v>
+        <v>58.1808645</v>
       </c>
       <c r="O6">
-        <v>18.670301312</v>
+        <v>18.61787664</v>
       </c>
       <c r="P6">
-        <v>39.674390288</v>
+        <v>39.56298786</v>
       </c>
       <c r="Q6">
-        <v>51.874390288</v>
+        <v>51.76298786</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1268610953616248</v>
+        <v>0.1274488453493189</v>
       </c>
       <c r="T6">
-        <v>0.4583659319247182</v>
+        <v>0.4616894075038022</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>90.03394432300881</v>
+        <v>72.02715545840705</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1227866030818529</v>
+        <v>0.1224183946165461</v>
       </c>
       <c r="C7">
-        <v>378.5141759086919</v>
+        <v>376.6767890154217</v>
       </c>
       <c r="D7">
-        <v>295.399175908692</v>
+        <v>296.8187890154217</v>
       </c>
       <c r="E7">
-        <v>-181.715</v>
+        <v>-178.458</v>
       </c>
       <c r="F7">
-        <v>16.285</v>
+        <v>19.54200000000001</v>
       </c>
       <c r="G7">
         <v>99.40000000000001</v>
@@ -1855,28 +1855,28 @@
         <v>59</v>
       </c>
       <c r="M7">
-        <v>0.8191355000000001</v>
+        <v>0.9829626000000002</v>
       </c>
       <c r="N7">
-        <v>58.1808645</v>
+        <v>58.0170374</v>
       </c>
       <c r="O7">
-        <v>18.61787664</v>
+        <v>18.565451968</v>
       </c>
       <c r="P7">
-        <v>39.56298786</v>
+        <v>39.451585432</v>
       </c>
       <c r="Q7">
-        <v>51.76298786</v>
+        <v>51.651585432</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1274488453493189</v>
+        <v>0.1280491006559001</v>
       </c>
       <c r="T7">
-        <v>0.4616894075038022</v>
+        <v>0.4650835953292496</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>72.02715545840705</v>
+        <v>60.02262954867254</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1224183946165461</v>
+        <v>0.1220501861512393</v>
       </c>
       <c r="C8">
-        <v>376.6767890154217</v>
+        <v>374.8531126083742</v>
       </c>
       <c r="D8">
-        <v>296.8187890154217</v>
+        <v>298.2521126083742</v>
       </c>
       <c r="E8">
-        <v>-178.458</v>
+        <v>-175.201</v>
       </c>
       <c r="F8">
-        <v>19.542</v>
+        <v>22.799</v>
       </c>
       <c r="G8">
         <v>99.40000000000001</v>
@@ -1937,28 +1937,28 @@
         <v>59</v>
       </c>
       <c r="M8">
-        <v>0.9829626</v>
+        <v>1.1467897</v>
       </c>
       <c r="N8">
-        <v>58.0170374</v>
+        <v>57.8532103</v>
       </c>
       <c r="O8">
-        <v>18.565451968</v>
+        <v>18.513027296</v>
       </c>
       <c r="P8">
-        <v>39.451585432</v>
+        <v>39.340183004</v>
       </c>
       <c r="Q8">
-        <v>51.651585432</v>
+        <v>51.540183004</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1280491006559001</v>
+        <v>0.1286622646787519</v>
       </c>
       <c r="T8">
-        <v>0.4650835953292496</v>
+        <v>0.4685507764412658</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>60.02262954867255</v>
+        <v>51.44796818457647</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1220501861512393</v>
+        <v>0.1216819776859325</v>
       </c>
       <c r="C9">
-        <v>374.8531126083744</v>
+        <v>373.0433462731659</v>
       </c>
       <c r="D9">
-        <v>298.2521126083744</v>
+        <v>299.6993462731659</v>
       </c>
       <c r="E9">
-        <v>-175.201</v>
+        <v>-171.944</v>
       </c>
       <c r="F9">
-        <v>22.79900000000001</v>
+        <v>26.056</v>
       </c>
       <c r="G9">
         <v>99.40000000000001</v>
@@ -2019,28 +2019,28 @@
         <v>59</v>
       </c>
       <c r="M9">
-        <v>1.1467897</v>
+        <v>1.3106168</v>
       </c>
       <c r="N9">
-        <v>57.8532103</v>
+        <v>57.6893832</v>
       </c>
       <c r="O9">
-        <v>18.513027296</v>
+        <v>18.460602624</v>
       </c>
       <c r="P9">
-        <v>39.340183004</v>
+        <v>39.22878057600001</v>
       </c>
       <c r="Q9">
-        <v>51.540183004</v>
+        <v>51.42878057600001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1286622646787519</v>
+        <v>0.1292887583542744</v>
       </c>
       <c r="T9">
-        <v>0.4685507764412658</v>
+        <v>0.4720933310557171</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>51.44796818457647</v>
+        <v>45.01697216150441</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1216819776859325</v>
+        <v>0.1213137692206256</v>
       </c>
       <c r="C10">
-        <v>373.0433462731659</v>
+        <v>371.2476934881659</v>
       </c>
       <c r="D10">
-        <v>299.6993462731659</v>
+        <v>301.1606934881658</v>
       </c>
       <c r="E10">
-        <v>-171.944</v>
+        <v>-168.687</v>
       </c>
       <c r="F10">
-        <v>26.056</v>
+        <v>29.313</v>
       </c>
       <c r="G10">
         <v>99.40000000000001</v>
@@ -2101,28 +2101,28 @@
         <v>59</v>
       </c>
       <c r="M10">
-        <v>1.3106168</v>
+        <v>1.4744439</v>
       </c>
       <c r="N10">
-        <v>57.6893832</v>
+        <v>57.5255561</v>
       </c>
       <c r="O10">
-        <v>18.460602624</v>
+        <v>18.408177952</v>
       </c>
       <c r="P10">
-        <v>39.22878057600001</v>
+        <v>39.117378148</v>
       </c>
       <c r="Q10">
-        <v>51.42878057600001</v>
+        <v>51.317378148</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1292887583542744</v>
+        <v>0.1299290211215666</v>
       </c>
       <c r="T10">
-        <v>0.4720933310557171</v>
+        <v>0.4757137440133432</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>45.01697216150441</v>
+        <v>40.01508636578171</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1213137692206256</v>
+        <v>0.1209455607553188</v>
       </c>
       <c r="C11">
-        <v>371.2476934881659</v>
+        <v>369.4663617198674</v>
       </c>
       <c r="D11">
-        <v>301.1606934881658</v>
+        <v>302.6363617198674</v>
       </c>
       <c r="E11">
-        <v>-168.687</v>
+        <v>-165.43</v>
       </c>
       <c r="F11">
-        <v>29.313</v>
+        <v>32.57</v>
       </c>
       <c r="G11">
         <v>99.40000000000001</v>
@@ -2183,28 +2183,28 @@
         <v>59</v>
       </c>
       <c r="M11">
-        <v>1.4744439</v>
+        <v>1.638271</v>
       </c>
       <c r="N11">
-        <v>57.5255561</v>
+        <v>57.361729</v>
       </c>
       <c r="O11">
-        <v>18.408177952</v>
+        <v>18.35575328</v>
       </c>
       <c r="P11">
-        <v>39.117378148</v>
+        <v>39.00597572</v>
       </c>
       <c r="Q11">
-        <v>51.317378148</v>
+        <v>51.20597572</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1299290211215666</v>
+        <v>0.1305835119503542</v>
       </c>
       <c r="T11">
-        <v>0.4757137440133432</v>
+        <v>0.4794146105922499</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>40.01508636578171</v>
+        <v>36.01357772920353</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1209455607553188</v>
+        <v>0.1205773522900119</v>
       </c>
       <c r="C12">
-        <v>369.4663617198674</v>
+        <v>367.699562521077</v>
       </c>
       <c r="D12">
-        <v>302.6363617198674</v>
+        <v>304.1265625210771</v>
       </c>
       <c r="E12">
-        <v>-165.43</v>
+        <v>-162.173</v>
       </c>
       <c r="F12">
-        <v>32.57000000000001</v>
+        <v>35.82700000000001</v>
       </c>
       <c r="G12">
         <v>99.40000000000001</v>
@@ -2265,28 +2265,28 @@
         <v>59</v>
       </c>
       <c r="M12">
-        <v>1.638271</v>
+        <v>1.8020981</v>
       </c>
       <c r="N12">
-        <v>57.361729</v>
+        <v>57.1979019</v>
       </c>
       <c r="O12">
-        <v>18.35575328</v>
+        <v>18.303328608</v>
       </c>
       <c r="P12">
-        <v>39.00597572</v>
+        <v>38.894573292</v>
       </c>
       <c r="Q12">
-        <v>51.20597572</v>
+        <v>51.09457329199999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1305835119503542</v>
+        <v>0.1312527104382157</v>
       </c>
       <c r="T12">
-        <v>0.4794146105922499</v>
+        <v>0.4831986427122555</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>36.01357772920353</v>
+        <v>32.73961611745775</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1205773522900119</v>
+        <v>0.1202091438247051</v>
       </c>
       <c r="C13">
-        <v>367.699562521077</v>
+        <v>365.9475116320189</v>
       </c>
       <c r="D13">
-        <v>304.1265625210771</v>
+        <v>305.6315116320189</v>
       </c>
       <c r="E13">
-        <v>-162.173</v>
+        <v>-158.916</v>
       </c>
       <c r="F13">
-        <v>35.82700000000001</v>
+        <v>39.084</v>
       </c>
       <c r="G13">
         <v>99.40000000000001</v>
@@ -2347,28 +2347,28 @@
         <v>59</v>
       </c>
       <c r="M13">
-        <v>1.8020981</v>
+        <v>1.9659252</v>
       </c>
       <c r="N13">
-        <v>57.1979019</v>
+        <v>57.0340748</v>
       </c>
       <c r="O13">
-        <v>18.303328608</v>
+        <v>18.250903936</v>
       </c>
       <c r="P13">
-        <v>38.894573292</v>
+        <v>38.783170864</v>
       </c>
       <c r="Q13">
-        <v>51.09457329199999</v>
+        <v>50.983170864</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1312527104382157</v>
+        <v>0.1319371179826194</v>
       </c>
       <c r="T13">
-        <v>0.4831986427122555</v>
+        <v>0.4870686755622614</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.73961611745775</v>
+        <v>30.01131477433628</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1202091438247051</v>
+        <v>0.1198409353593982</v>
       </c>
       <c r="C14">
-        <v>365.9475116320189</v>
+        <v>364.210429084455</v>
       </c>
       <c r="D14">
-        <v>305.6315116320189</v>
+        <v>307.151429084455</v>
       </c>
       <c r="E14">
-        <v>-158.916</v>
+        <v>-155.659</v>
       </c>
       <c r="F14">
-        <v>39.084</v>
+        <v>42.34100000000001</v>
       </c>
       <c r="G14">
         <v>99.40000000000001</v>
@@ -2429,28 +2429,28 @@
         <v>59</v>
       </c>
       <c r="M14">
-        <v>1.9659252</v>
+        <v>2.1297523</v>
       </c>
       <c r="N14">
-        <v>57.0340748</v>
+        <v>56.8702477</v>
       </c>
       <c r="O14">
-        <v>18.250903936</v>
+        <v>18.198479264</v>
       </c>
       <c r="P14">
-        <v>38.783170864</v>
+        <v>38.671768436</v>
       </c>
       <c r="Q14">
-        <v>50.983170864</v>
+        <v>50.871768436</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1319371179826194</v>
+        <v>0.1326372590337911</v>
       </c>
       <c r="T14">
-        <v>0.4870686755622614</v>
+        <v>0.4910276746846811</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>30.01131477433628</v>
+        <v>27.70275209938733</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1198409353593982</v>
+        <v>0.1194727268940914</v>
       </c>
       <c r="C15">
-        <v>364.210429084455</v>
+        <v>362.4885393089288</v>
       </c>
       <c r="D15">
-        <v>307.151429084455</v>
+        <v>308.6865393089288</v>
       </c>
       <c r="E15">
-        <v>-155.659</v>
+        <v>-152.402</v>
       </c>
       <c r="F15">
-        <v>42.34100000000001</v>
+        <v>45.59800000000001</v>
       </c>
       <c r="G15">
         <v>99.40000000000001</v>
@@ -2511,28 +2511,28 @@
         <v>59</v>
       </c>
       <c r="M15">
-        <v>2.1297523</v>
+        <v>2.2935794</v>
       </c>
       <c r="N15">
-        <v>56.8702477</v>
+        <v>56.7064206</v>
       </c>
       <c r="O15">
-        <v>18.198479264</v>
+        <v>18.146054592</v>
       </c>
       <c r="P15">
-        <v>38.671768436</v>
+        <v>38.560366008</v>
       </c>
       <c r="Q15">
-        <v>50.871768436</v>
+        <v>50.76036600800001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1326372590337911</v>
+        <v>0.13335368243499</v>
       </c>
       <c r="T15">
-        <v>0.4910276746846811</v>
+        <v>0.4950787435541338</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.70275209938733</v>
+        <v>25.72398409228823</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1194727268940914</v>
+        <v>0.1191045184287846</v>
       </c>
       <c r="C16">
-        <v>362.4885393089288</v>
+        <v>360.782071245241</v>
       </c>
       <c r="D16">
-        <v>308.6865393089288</v>
+        <v>310.2370712452411</v>
       </c>
       <c r="E16">
-        <v>-152.402</v>
+        <v>-149.145</v>
       </c>
       <c r="F16">
-        <v>45.59800000000001</v>
+        <v>48.85500000000001</v>
       </c>
       <c r="G16">
         <v>99.40000000000001</v>
@@ -2593,28 +2593,28 @@
         <v>59</v>
       </c>
       <c r="M16">
-        <v>2.2935794</v>
+        <v>2.4574065</v>
       </c>
       <c r="N16">
-        <v>56.7064206</v>
+        <v>56.5425935</v>
       </c>
       <c r="O16">
-        <v>18.146054592</v>
+        <v>18.09362992</v>
       </c>
       <c r="P16">
-        <v>38.560366008</v>
+        <v>38.44896358</v>
       </c>
       <c r="Q16">
-        <v>50.76036600800001</v>
+        <v>50.64896358</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.13335368243499</v>
+        <v>0.1340869628573936</v>
       </c>
       <c r="T16">
-        <v>0.4950787435541338</v>
+        <v>0.4992251316911032</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.72398409228823</v>
+        <v>24.00905181946902</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1191045184287846</v>
+        <v>0.1187363099634777</v>
       </c>
       <c r="C17">
-        <v>360.782071245241</v>
+        <v>359.0912584562707</v>
       </c>
       <c r="D17">
-        <v>310.2370712452411</v>
+        <v>311.8032584562708</v>
       </c>
       <c r="E17">
-        <v>-149.145</v>
+        <v>-145.888</v>
       </c>
       <c r="F17">
-        <v>48.855</v>
+        <v>52.11200000000001</v>
       </c>
       <c r="G17">
         <v>99.40000000000001</v>
@@ -2675,28 +2675,28 @@
         <v>59</v>
       </c>
       <c r="M17">
-        <v>2.4574065</v>
+        <v>2.6212336</v>
       </c>
       <c r="N17">
-        <v>56.5425935</v>
+        <v>56.3787664</v>
       </c>
       <c r="O17">
-        <v>18.09362992</v>
+        <v>18.041205248</v>
       </c>
       <c r="P17">
-        <v>38.44896358</v>
+        <v>38.33756115199999</v>
       </c>
       <c r="Q17">
-        <v>50.64896358</v>
+        <v>50.53756115199999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1340869628573936</v>
+        <v>0.1348377023374735</v>
       </c>
       <c r="T17">
-        <v>0.4992251316911032</v>
+        <v>0.5034702433551431</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>24.00905181946902</v>
+        <v>22.5084860807522</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1187363099634777</v>
+        <v>0.1183681014981709</v>
       </c>
       <c r="C18">
-        <v>359.0912584562707</v>
+        <v>357.4163392452624</v>
       </c>
       <c r="D18">
-        <v>311.8032584562708</v>
+        <v>313.3853392452624</v>
       </c>
       <c r="E18">
-        <v>-145.888</v>
+        <v>-142.631</v>
       </c>
       <c r="F18">
-        <v>52.11200000000001</v>
+        <v>55.36900000000001</v>
       </c>
       <c r="G18">
         <v>99.40000000000001</v>
@@ -2757,28 +2757,28 @@
         <v>59</v>
       </c>
       <c r="M18">
-        <v>2.6212336</v>
+        <v>2.785060700000001</v>
       </c>
       <c r="N18">
-        <v>56.3787664</v>
+        <v>56.2149393</v>
       </c>
       <c r="O18">
-        <v>18.041205248</v>
+        <v>17.988780576</v>
       </c>
       <c r="P18">
-        <v>38.33756115199999</v>
+        <v>38.226158724</v>
       </c>
       <c r="Q18">
-        <v>50.53756115199999</v>
+        <v>50.426158724</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1348377023374735</v>
+        <v>0.1356065319255071</v>
       </c>
       <c r="T18">
-        <v>0.5034702433551431</v>
+        <v>0.5078176468665094</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.5084860807522</v>
+        <v>21.18445748776678</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1183681014981709</v>
+        <v>0.1179998930328641</v>
       </c>
       <c r="C19">
-        <v>357.4163392452624</v>
+        <v>355.7575567767016</v>
       </c>
       <c r="D19">
-        <v>313.3853392452624</v>
+        <v>314.9835567767017</v>
       </c>
       <c r="E19">
-        <v>-142.631</v>
+        <v>-139.374</v>
       </c>
       <c r="F19">
-        <v>55.36900000000001</v>
+        <v>58.62600000000001</v>
       </c>
       <c r="G19">
         <v>99.40000000000001</v>
@@ -2839,28 +2839,28 @@
         <v>59</v>
       </c>
       <c r="M19">
-        <v>2.785060700000001</v>
+        <v>2.948887800000001</v>
       </c>
       <c r="N19">
-        <v>56.2149393</v>
+        <v>56.0511122</v>
       </c>
       <c r="O19">
-        <v>17.988780576</v>
+        <v>17.936355904</v>
       </c>
       <c r="P19">
-        <v>38.226158724</v>
+        <v>38.114756296</v>
       </c>
       <c r="Q19">
-        <v>50.426158724</v>
+        <v>50.314756296</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1356065319255071</v>
+        <v>0.1363941134547123</v>
       </c>
       <c r="T19">
-        <v>0.5078176468665094</v>
+        <v>0.5122710846098602</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>21.18445748776678</v>
+        <v>20.00754318289085</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1179998930328641</v>
+        <v>0.1176316845675573</v>
       </c>
       <c r="C20">
-        <v>355.7575567767017</v>
+        <v>354.1151592009084</v>
       </c>
       <c r="D20">
-        <v>314.9835567767016</v>
+        <v>316.5981592009084</v>
       </c>
       <c r="E20">
-        <v>-139.374</v>
+        <v>-136.117</v>
       </c>
       <c r="F20">
-        <v>58.626</v>
+        <v>61.88300000000001</v>
       </c>
       <c r="G20">
         <v>99.40000000000001</v>
@@ -2921,28 +2921,28 @@
         <v>59</v>
       </c>
       <c r="M20">
-        <v>2.9488878</v>
+        <v>3.1127149</v>
       </c>
       <c r="N20">
-        <v>56.0511122</v>
+        <v>55.8872851</v>
       </c>
       <c r="O20">
-        <v>17.936355904</v>
+        <v>17.883931232</v>
       </c>
       <c r="P20">
-        <v>38.114756296</v>
+        <v>38.003353868</v>
       </c>
       <c r="Q20">
-        <v>50.314756296</v>
+        <v>50.20335386799999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1363941134547123</v>
+        <v>0.1372011414414287</v>
       </c>
       <c r="T20">
-        <v>0.5122710846098602</v>
+        <v>0.5168344837789728</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>20.00754318289085</v>
+        <v>18.95451459431765</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1176316845675573</v>
+        <v>0.1172634761022504</v>
       </c>
       <c r="C21">
-        <v>354.1151592009084</v>
+        <v>352.4893997824826</v>
       </c>
       <c r="D21">
-        <v>316.5981592009084</v>
+        <v>318.2293997824826</v>
       </c>
       <c r="E21">
-        <v>-136.117</v>
+        <v>-132.86</v>
       </c>
       <c r="F21">
-        <v>61.88300000000001</v>
+        <v>65.14000000000001</v>
       </c>
       <c r="G21">
         <v>99.40000000000001</v>
@@ -3003,28 +3003,28 @@
         <v>59</v>
       </c>
       <c r="M21">
-        <v>3.1127149</v>
+        <v>3.276542000000001</v>
       </c>
       <c r="N21">
-        <v>55.8872851</v>
+        <v>55.723458</v>
       </c>
       <c r="O21">
-        <v>17.883931232</v>
+        <v>17.83150656</v>
       </c>
       <c r="P21">
-        <v>38.003353868</v>
+        <v>37.89195144</v>
       </c>
       <c r="Q21">
-        <v>50.20335386799999</v>
+        <v>50.09195144</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1372011414414287</v>
+        <v>0.138028345127813</v>
       </c>
       <c r="T21">
-        <v>0.5168344837789728</v>
+        <v>0.521511967927313</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.95451459431765</v>
+        <v>18.00678886460176</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1172634761022504</v>
+        <v>0.1168952676369436</v>
       </c>
       <c r="C22">
-        <v>352.4893997824826</v>
+        <v>350.8805370327392</v>
       </c>
       <c r="D22">
-        <v>318.2293997824826</v>
+        <v>319.8775370327393</v>
       </c>
       <c r="E22">
-        <v>-132.86</v>
+        <v>-129.603</v>
       </c>
       <c r="F22">
-        <v>65.14000000000001</v>
+        <v>68.39700000000002</v>
       </c>
       <c r="G22">
         <v>99.40000000000001</v>
@@ -3085,28 +3085,28 @@
         <v>59</v>
       </c>
       <c r="M22">
-        <v>3.276542000000001</v>
+        <v>3.440369100000001</v>
       </c>
       <c r="N22">
-        <v>55.723458</v>
+        <v>55.5596309</v>
       </c>
       <c r="O22">
-        <v>17.83150656</v>
+        <v>17.779081888</v>
       </c>
       <c r="P22">
-        <v>37.89195144</v>
+        <v>37.780549012</v>
       </c>
       <c r="Q22">
-        <v>50.09195144</v>
+        <v>49.980549012</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.138028345127813</v>
+        <v>0.1388764906796754</v>
       </c>
       <c r="T22">
-        <v>0.521511967927313</v>
+        <v>0.5263078693958646</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.00678886460176</v>
+        <v>17.14932272819216</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1168952676369436</v>
+        <v>0.1165270591716367</v>
       </c>
       <c r="C23">
-        <v>350.8805370327393</v>
+        <v>349.2888348462839</v>
       </c>
       <c r="D23">
-        <v>319.8775370327393</v>
+        <v>321.5428348462838</v>
       </c>
       <c r="E23">
-        <v>-129.603</v>
+        <v>-126.346</v>
       </c>
       <c r="F23">
-        <v>68.39700000000001</v>
+        <v>71.65400000000001</v>
       </c>
       <c r="G23">
         <v>99.40000000000001</v>
@@ -3167,28 +3167,28 @@
         <v>59</v>
       </c>
       <c r="M23">
-        <v>3.4403691</v>
+        <v>3.604196200000001</v>
       </c>
       <c r="N23">
-        <v>55.5596309</v>
+        <v>55.3958038</v>
       </c>
       <c r="O23">
-        <v>17.779081888</v>
+        <v>17.726657216</v>
       </c>
       <c r="P23">
-        <v>37.780549012</v>
+        <v>37.669146584</v>
       </c>
       <c r="Q23">
-        <v>49.980549012</v>
+        <v>49.86914658399999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1388764906796754</v>
+        <v>0.1397463835533804</v>
       </c>
       <c r="T23">
-        <v>0.5263078693958646</v>
+        <v>0.5312267426969431</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.14932272819216</v>
+        <v>16.36980805872888</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1165270591716367</v>
+        <v>0.1161588507063299</v>
       </c>
       <c r="C24">
-        <v>349.2888348462839</v>
+        <v>347.7145626418717</v>
       </c>
       <c r="D24">
-        <v>321.5428348462838</v>
+        <v>323.2255626418718</v>
       </c>
       <c r="E24">
-        <v>-126.346</v>
+        <v>-123.089</v>
       </c>
       <c r="F24">
-        <v>71.65400000000001</v>
+        <v>74.91100000000002</v>
       </c>
       <c r="G24">
         <v>99.40000000000001</v>
@@ -3249,28 +3249,28 @@
         <v>59</v>
       </c>
       <c r="M24">
-        <v>3.604196200000001</v>
+        <v>3.768023300000001</v>
       </c>
       <c r="N24">
-        <v>55.3958038</v>
+        <v>55.2319767</v>
       </c>
       <c r="O24">
-        <v>17.726657216</v>
+        <v>17.674232544</v>
       </c>
       <c r="P24">
-        <v>37.669146584</v>
+        <v>37.557744156</v>
       </c>
       <c r="Q24">
-        <v>49.86914658399999</v>
+        <v>49.757744156</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1397463835533804</v>
+        <v>0.1406388710471816</v>
       </c>
       <c r="T24">
-        <v>0.5312267426969431</v>
+        <v>0.5362733789409067</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.36980805872888</v>
+        <v>15.65807727356675</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1161588507063299</v>
+        <v>0.115790642241023</v>
       </c>
       <c r="C25">
-        <v>347.7145626418717</v>
+        <v>346.1579955077177</v>
       </c>
       <c r="D25">
-        <v>323.2255626418718</v>
+        <v>324.9259955077177</v>
       </c>
       <c r="E25">
-        <v>-123.089</v>
+        <v>-119.832</v>
       </c>
       <c r="F25">
-        <v>74.91100000000002</v>
+        <v>78.16800000000002</v>
       </c>
       <c r="G25">
         <v>99.40000000000001</v>
@@ -3331,28 +3331,28 @@
         <v>59</v>
       </c>
       <c r="M25">
-        <v>3.768023300000001</v>
+        <v>3.931850400000001</v>
       </c>
       <c r="N25">
-        <v>55.2319767</v>
+        <v>55.0681496</v>
       </c>
       <c r="O25">
-        <v>17.674232544</v>
+        <v>17.621807872</v>
       </c>
       <c r="P25">
-        <v>37.557744156</v>
+        <v>37.44634172799999</v>
       </c>
       <c r="Q25">
-        <v>49.757744156</v>
+        <v>49.646341728</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1406388710471816</v>
+        <v>0.1415548450539777</v>
       </c>
       <c r="T25">
-        <v>0.5362733789409067</v>
+        <v>0.5414528214018167</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.65807727356675</v>
+        <v>15.00565738716814</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.115790642241023</v>
+        <v>0.1154224337757162</v>
       </c>
       <c r="C26">
-        <v>346.1579955077177</v>
+        <v>344.6194143514142</v>
       </c>
       <c r="D26">
-        <v>324.9259955077177</v>
+        <v>326.6444143514142</v>
       </c>
       <c r="E26">
-        <v>-119.832</v>
+        <v>-116.575</v>
       </c>
       <c r="F26">
-        <v>78.16800000000001</v>
+        <v>81.42500000000001</v>
       </c>
       <c r="G26">
         <v>99.40000000000001</v>
@@ -3413,28 +3413,28 @@
         <v>59</v>
       </c>
       <c r="M26">
-        <v>3.9318504</v>
+        <v>4.095677500000001</v>
       </c>
       <c r="N26">
-        <v>55.0681496</v>
+        <v>54.9043225</v>
       </c>
       <c r="O26">
-        <v>17.621807872</v>
+        <v>17.5693832</v>
       </c>
       <c r="P26">
-        <v>37.44634172799999</v>
+        <v>37.3349393</v>
       </c>
       <c r="Q26">
-        <v>49.646341728</v>
+        <v>49.5349393</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1415548450539777</v>
+        <v>0.1424952450342882</v>
       </c>
       <c r="T26">
-        <v>0.5414528214018167</v>
+        <v>0.546770382328351</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.00565738716814</v>
+        <v>14.40543109168141</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1154224337757162</v>
+        <v>0.1150542253104093</v>
       </c>
       <c r="C27">
-        <v>344.6194143514142</v>
+        <v>343.0991060546322</v>
       </c>
       <c r="D27">
-        <v>326.6444143514142</v>
+        <v>328.3811060546322</v>
       </c>
       <c r="E27">
-        <v>-116.575</v>
+        <v>-113.318</v>
       </c>
       <c r="F27">
-        <v>81.42500000000001</v>
+        <v>84.68200000000002</v>
       </c>
       <c r="G27">
         <v>99.40000000000001</v>
@@ -3495,28 +3495,28 @@
         <v>59</v>
       </c>
       <c r="M27">
-        <v>4.095677500000001</v>
+        <v>4.259504600000001</v>
       </c>
       <c r="N27">
-        <v>54.9043225</v>
+        <v>54.7404954</v>
       </c>
       <c r="O27">
-        <v>17.5693832</v>
+        <v>17.516958528</v>
       </c>
       <c r="P27">
-        <v>37.3349393</v>
+        <v>37.223536872</v>
       </c>
       <c r="Q27">
-        <v>49.5349393</v>
+        <v>49.423536872</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1424952450342882</v>
+        <v>0.1434610612302829</v>
       </c>
       <c r="T27">
-        <v>0.546770382328351</v>
+        <v>0.5522316611177647</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.40543109168141</v>
+        <v>13.85137604969366</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1150542253104093</v>
+        <v>0.1146860168451025</v>
       </c>
       <c r="C28">
-        <v>343.0991060546322</v>
+        <v>341.5973636327851</v>
       </c>
       <c r="D28">
-        <v>328.3811060546322</v>
+        <v>330.1363636327851</v>
       </c>
       <c r="E28">
-        <v>-113.318</v>
+        <v>-110.061</v>
       </c>
       <c r="F28">
-        <v>84.68200000000002</v>
+        <v>87.93900000000002</v>
       </c>
       <c r="G28">
         <v>99.40000000000001</v>
@@ -3577,28 +3577,28 @@
         <v>59</v>
       </c>
       <c r="M28">
-        <v>4.259504600000001</v>
+        <v>4.423331700000001</v>
       </c>
       <c r="N28">
-        <v>54.7404954</v>
+        <v>54.5766683</v>
       </c>
       <c r="O28">
-        <v>17.516958528</v>
+        <v>17.464533856</v>
       </c>
       <c r="P28">
-        <v>37.223536872</v>
+        <v>37.11213444400001</v>
       </c>
       <c r="Q28">
-        <v>49.423536872</v>
+        <v>49.31213444400001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1434610612302829</v>
+        <v>0.144453338143976</v>
       </c>
       <c r="T28">
-        <v>0.5522316611177647</v>
+        <v>0.5578425639836005</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.85137604969366</v>
+        <v>13.33836212192723</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1146860168451025</v>
+        <v>0.1146034083797957</v>
       </c>
       <c r="C29">
-        <v>341.5973636327851</v>
+        <v>338.736740192957</v>
       </c>
       <c r="D29">
-        <v>330.1363636327851</v>
+        <v>330.532740192957</v>
       </c>
       <c r="E29">
-        <v>-110.061</v>
+        <v>-106.804</v>
       </c>
       <c r="F29">
-        <v>87.93900000000002</v>
+        <v>91.19600000000003</v>
       </c>
       <c r="G29">
         <v>99.40000000000001</v>
@@ -3659,45 +3659,45 @@
         <v>59</v>
       </c>
       <c r="M29">
-        <v>4.423331700000001</v>
+        <v>4.723952800000001</v>
       </c>
       <c r="N29">
-        <v>54.5766683</v>
+        <v>54.2760472</v>
       </c>
       <c r="O29">
-        <v>17.464533856</v>
+        <v>17.368335104</v>
       </c>
       <c r="P29">
-        <v>37.11213444400001</v>
+        <v>36.907712096</v>
       </c>
       <c r="Q29">
-        <v>49.31213444400001</v>
+        <v>49.107712096</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.144453338143976</v>
+        <v>0.1454731783052718</v>
       </c>
       <c r="T29">
-        <v>0.5578425639836005</v>
+        <v>0.5636093252623764</v>
       </c>
       <c r="U29">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0.32</v>
       </c>
       <c r="W29">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>13.33836212192723</v>
+        <v>12.48954053901639</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1146034083797957</v>
+        <v>0.1142453999144888</v>
       </c>
       <c r="C30">
-        <v>338.736740192957</v>
+        <v>337.2086148755213</v>
       </c>
       <c r="D30">
-        <v>330.532740192957</v>
+        <v>332.2616148755213</v>
       </c>
       <c r="E30">
-        <v>-106.804</v>
+        <v>-103.547</v>
       </c>
       <c r="F30">
-        <v>91.19600000000003</v>
+        <v>94.45300000000003</v>
       </c>
       <c r="G30">
         <v>99.40000000000001</v>
@@ -3741,28 +3741,28 @@
         <v>59</v>
       </c>
       <c r="M30">
-        <v>4.723952800000001</v>
+        <v>4.892665400000001</v>
       </c>
       <c r="N30">
-        <v>54.2760472</v>
+        <v>54.1073346</v>
       </c>
       <c r="O30">
-        <v>17.368335104</v>
+        <v>17.314347072</v>
       </c>
       <c r="P30">
-        <v>36.907712096</v>
+        <v>36.792987528</v>
       </c>
       <c r="Q30">
-        <v>49.107712096</v>
+        <v>48.992987528</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1454731783052718</v>
+        <v>0.146521746358435</v>
       </c>
       <c r="T30">
-        <v>0.5636093252623764</v>
+        <v>0.5695385305208359</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.48954053901639</v>
+        <v>12.05886672732617</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1142453999144888</v>
+        <v>0.113887391449182</v>
       </c>
       <c r="C31">
-        <v>337.2086148755213</v>
+        <v>335.6986706561902</v>
       </c>
       <c r="D31">
-        <v>332.2616148755213</v>
+        <v>334.0086706561902</v>
       </c>
       <c r="E31">
-        <v>-103.547</v>
+        <v>-100.29</v>
       </c>
       <c r="F31">
-        <v>94.453</v>
+        <v>97.71000000000001</v>
       </c>
       <c r="G31">
         <v>99.40000000000001</v>
@@ -3823,28 +3823,28 @@
         <v>59</v>
       </c>
       <c r="M31">
-        <v>4.8926654</v>
+        <v>5.061378</v>
       </c>
       <c r="N31">
-        <v>54.1073346</v>
+        <v>53.938622</v>
       </c>
       <c r="O31">
-        <v>17.314347072</v>
+        <v>17.26035904</v>
       </c>
       <c r="P31">
-        <v>36.792987528</v>
+        <v>36.67826296</v>
       </c>
       <c r="Q31">
-        <v>48.992987528</v>
+        <v>48.87826296</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.146521746358435</v>
+        <v>0.1476002734988314</v>
       </c>
       <c r="T31">
-        <v>0.5695385305208359</v>
+        <v>0.575637141643823</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>12.05886672732617</v>
+        <v>11.65690450308197</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.113887391449182</v>
+        <v>0.1135293829838751</v>
       </c>
       <c r="C32">
-        <v>335.6986706561902</v>
+        <v>334.2071958435268</v>
       </c>
       <c r="D32">
-        <v>334.0086706561902</v>
+        <v>335.7741958435268</v>
       </c>
       <c r="E32">
-        <v>-100.29</v>
+        <v>-97.03300000000002</v>
       </c>
       <c r="F32">
-        <v>97.71000000000001</v>
+        <v>100.967</v>
       </c>
       <c r="G32">
         <v>99.40000000000001</v>
@@ -3905,28 +3905,28 @@
         <v>59</v>
       </c>
       <c r="M32">
-        <v>5.061378</v>
+        <v>5.2300906</v>
       </c>
       <c r="N32">
-        <v>53.938622</v>
+        <v>53.7699094</v>
       </c>
       <c r="O32">
-        <v>17.26035904</v>
+        <v>17.206371008</v>
       </c>
       <c r="P32">
-        <v>36.67826296</v>
+        <v>36.563538392</v>
       </c>
       <c r="Q32">
-        <v>48.87826296</v>
+        <v>48.763538392</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1476002734988314</v>
+        <v>0.1487100622954712</v>
       </c>
       <c r="T32">
-        <v>0.575637141643823</v>
+        <v>0.5819125241037082</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.65690450308197</v>
+        <v>11.28087532556319</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1135293829838751</v>
+        <v>0.1131713745185683</v>
       </c>
       <c r="C33">
-        <v>334.2071958435268</v>
+        <v>332.7344848743294</v>
       </c>
       <c r="D33">
-        <v>335.7741958435268</v>
+        <v>337.5584848743295</v>
       </c>
       <c r="E33">
-        <v>-97.03300000000002</v>
+        <v>-93.77600000000001</v>
       </c>
       <c r="F33">
-        <v>100.967</v>
+        <v>104.224</v>
       </c>
       <c r="G33">
         <v>99.40000000000001</v>
@@ -3987,28 +3987,28 @@
         <v>59</v>
       </c>
       <c r="M33">
-        <v>5.2300906</v>
+        <v>5.398803200000001</v>
       </c>
       <c r="N33">
-        <v>53.7699094</v>
+        <v>53.6011968</v>
       </c>
       <c r="O33">
-        <v>17.206371008</v>
+        <v>17.152382976</v>
       </c>
       <c r="P33">
-        <v>36.563538392</v>
+        <v>36.448813824</v>
       </c>
       <c r="Q33">
-        <v>48.763538392</v>
+        <v>48.648813824</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1487100622954712</v>
+        <v>0.1498524919390711</v>
       </c>
       <c r="T33">
-        <v>0.5819125241037082</v>
+        <v>0.5883724766359431</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.28087532556319</v>
+        <v>10.92834797163934</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1131713745185683</v>
+        <v>0.1128133660532615</v>
       </c>
       <c r="C34">
-        <v>332.7344848743294</v>
+        <v>331.2808384773273</v>
       </c>
       <c r="D34">
-        <v>337.5584848743295</v>
+        <v>339.3618384773272</v>
       </c>
       <c r="E34">
-        <v>-93.77600000000001</v>
+        <v>-90.51900000000001</v>
       </c>
       <c r="F34">
-        <v>104.224</v>
+        <v>107.481</v>
       </c>
       <c r="G34">
         <v>99.40000000000001</v>
@@ -4069,28 +4069,28 @@
         <v>59</v>
       </c>
       <c r="M34">
-        <v>5.398803200000001</v>
+        <v>5.567515800000001</v>
       </c>
       <c r="N34">
-        <v>53.6011968</v>
+        <v>53.4324842</v>
       </c>
       <c r="O34">
-        <v>17.152382976</v>
+        <v>17.098394944</v>
       </c>
       <c r="P34">
-        <v>36.448813824</v>
+        <v>36.334089256</v>
       </c>
       <c r="Q34">
-        <v>48.648813824</v>
+        <v>48.534089256</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1498524919390711</v>
+        <v>0.1510290239600918</v>
       </c>
       <c r="T34">
-        <v>0.5883724766359431</v>
+        <v>0.5950252635721252</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.92834797163934</v>
+        <v>10.5971859118927</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1128133660532615</v>
+        <v>0.1124553575879546</v>
       </c>
       <c r="C35">
-        <v>331.2808384773273</v>
+        <v>329.8465638421511</v>
       </c>
       <c r="D35">
-        <v>339.3618384773272</v>
+        <v>341.1845638421511</v>
       </c>
       <c r="E35">
-        <v>-90.51900000000001</v>
+        <v>-87.262</v>
       </c>
       <c r="F35">
-        <v>107.481</v>
+        <v>110.738</v>
       </c>
       <c r="G35">
         <v>99.40000000000001</v>
@@ -4151,28 +4151,28 @@
         <v>59</v>
       </c>
       <c r="M35">
-        <v>5.567515800000001</v>
+        <v>5.736228400000002</v>
       </c>
       <c r="N35">
-        <v>53.4324842</v>
+        <v>53.2637716</v>
       </c>
       <c r="O35">
-        <v>17.098394944</v>
+        <v>17.044406912</v>
       </c>
       <c r="P35">
-        <v>36.334089256</v>
+        <v>36.219364688</v>
       </c>
       <c r="Q35">
-        <v>48.534089256</v>
+        <v>48.419364688</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1510290239600918</v>
+        <v>0.152241208466598</v>
       </c>
       <c r="T35">
-        <v>0.5950252635721252</v>
+        <v>0.6018796501124339</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.5971859118927</v>
+        <v>10.28550397330761</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1124553575879546</v>
+        <v>0.1120973491226478</v>
       </c>
       <c r="C36">
-        <v>329.8465638421511</v>
+        <v>328.4319747937799</v>
       </c>
       <c r="D36">
-        <v>341.1845638421511</v>
+        <v>343.0269747937799</v>
       </c>
       <c r="E36">
-        <v>-87.262</v>
+        <v>-84.005</v>
       </c>
       <c r="F36">
-        <v>110.738</v>
+        <v>113.995</v>
       </c>
       <c r="G36">
         <v>99.40000000000001</v>
@@ -4233,28 +4233,28 @@
         <v>59</v>
       </c>
       <c r="M36">
-        <v>5.736228400000002</v>
+        <v>5.904941000000002</v>
       </c>
       <c r="N36">
-        <v>53.2637716</v>
+        <v>53.095059</v>
       </c>
       <c r="O36">
-        <v>17.044406912</v>
+        <v>16.99041888</v>
       </c>
       <c r="P36">
-        <v>36.219364688</v>
+        <v>36.10464012</v>
       </c>
       <c r="Q36">
-        <v>48.419364688</v>
+        <v>48.30464012</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.152241208466598</v>
+        <v>0.1534906909579197</v>
       </c>
       <c r="T36">
-        <v>0.6018796501124339</v>
+        <v>0.608944940853983</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.28550397330761</v>
+        <v>9.991632431213112</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1120973491226478</v>
+        <v>0.112155500657341</v>
       </c>
       <c r="C37">
-        <v>328.4319747937799</v>
+        <v>324.8743584947871</v>
       </c>
       <c r="D37">
-        <v>343.0269747937799</v>
+        <v>342.7263584947871</v>
       </c>
       <c r="E37">
-        <v>-84.005</v>
+        <v>-80.748</v>
       </c>
       <c r="F37">
-        <v>113.995</v>
+        <v>117.252</v>
       </c>
       <c r="G37">
         <v>99.40000000000001</v>
@@ -4315,45 +4315,45 @@
         <v>59</v>
       </c>
       <c r="M37">
-        <v>5.904941000000002</v>
+        <v>6.272982000000001</v>
       </c>
       <c r="N37">
-        <v>53.095059</v>
+        <v>52.727018</v>
       </c>
       <c r="O37">
-        <v>16.99041888</v>
+        <v>16.87264576</v>
       </c>
       <c r="P37">
-        <v>36.10464012</v>
+        <v>35.85437224</v>
       </c>
       <c r="Q37">
-        <v>48.30464012</v>
+        <v>48.05437224000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1534906909579197</v>
+        <v>0.1547792197770953</v>
       </c>
       <c r="T37">
-        <v>0.608944940853983</v>
+        <v>0.6162310219312055</v>
       </c>
       <c r="U37">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V37">
         <v>0.32</v>
       </c>
       <c r="W37">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>9.991632431213112</v>
+        <v>9.405415159807568</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.112155500657341</v>
+        <v>0.1118090521920341</v>
       </c>
       <c r="C38">
-        <v>324.8743584947873</v>
+        <v>323.4161575530632</v>
       </c>
       <c r="D38">
-        <v>342.7263584947872</v>
+        <v>344.5251575530631</v>
       </c>
       <c r="E38">
-        <v>-80.74800000000002</v>
+        <v>-77.49100000000001</v>
       </c>
       <c r="F38">
-        <v>117.252</v>
+        <v>120.509</v>
       </c>
       <c r="G38">
         <v>99.40000000000001</v>
@@ -4397,28 +4397,28 @@
         <v>59</v>
       </c>
       <c r="M38">
-        <v>6.272982000000001</v>
+        <v>6.447231500000001</v>
       </c>
       <c r="N38">
-        <v>52.727018</v>
+        <v>52.5527685</v>
       </c>
       <c r="O38">
-        <v>16.87264576</v>
+        <v>16.81688592</v>
       </c>
       <c r="P38">
-        <v>35.85437224</v>
+        <v>35.73588257999999</v>
       </c>
       <c r="Q38">
-        <v>48.05437224000001</v>
+        <v>47.93588258</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1547792197770952</v>
+        <v>0.15610865427307</v>
       </c>
       <c r="T38">
-        <v>0.6162310219312054</v>
+        <v>0.6237484071696096</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.405415159807568</v>
+        <v>9.151214750083039</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1118090521920341</v>
+        <v>0.1114626037267273</v>
       </c>
       <c r="C39">
-        <v>323.4161575530632</v>
+        <v>321.9769382275944</v>
       </c>
       <c r="D39">
-        <v>344.5251575530631</v>
+        <v>346.3429382275945</v>
       </c>
       <c r="E39">
-        <v>-77.49100000000001</v>
+        <v>-74.23400000000001</v>
       </c>
       <c r="F39">
-        <v>120.509</v>
+        <v>123.766</v>
       </c>
       <c r="G39">
         <v>99.40000000000001</v>
@@ -4479,28 +4479,28 @@
         <v>59</v>
       </c>
       <c r="M39">
-        <v>6.447231500000001</v>
+        <v>6.621481000000001</v>
       </c>
       <c r="N39">
-        <v>52.5527685</v>
+        <v>52.378519</v>
       </c>
       <c r="O39">
-        <v>16.81688592</v>
+        <v>16.76112608</v>
       </c>
       <c r="P39">
-        <v>35.73588257999999</v>
+        <v>35.61739292</v>
       </c>
       <c r="Q39">
-        <v>47.93588258</v>
+        <v>47.81739292</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.15610865427307</v>
+        <v>0.157480973752786</v>
       </c>
       <c r="T39">
-        <v>0.6237484071696096</v>
+        <v>0.6315082887060268</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.151214750083039</v>
+        <v>8.910393309291379</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1114626037267273</v>
+        <v>0.1111161552614204</v>
       </c>
       <c r="C40">
-        <v>321.9769382275944</v>
+        <v>320.5570025639531</v>
       </c>
       <c r="D40">
-        <v>346.3429382275945</v>
+        <v>348.1800025639531</v>
       </c>
       <c r="E40">
-        <v>-74.23400000000001</v>
+        <v>-70.977</v>
       </c>
       <c r="F40">
-        <v>123.766</v>
+        <v>127.023</v>
       </c>
       <c r="G40">
         <v>99.40000000000001</v>
@@ -4561,28 +4561,28 @@
         <v>59</v>
       </c>
       <c r="M40">
-        <v>6.621481000000001</v>
+        <v>6.795730500000001</v>
       </c>
       <c r="N40">
-        <v>52.378519</v>
+        <v>52.2042695</v>
       </c>
       <c r="O40">
-        <v>16.76112608</v>
+        <v>16.70536624</v>
       </c>
       <c r="P40">
-        <v>35.61739292</v>
+        <v>35.49890325999999</v>
       </c>
       <c r="Q40">
-        <v>47.81739292</v>
+        <v>47.69890325999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.157480973752786</v>
+        <v>0.158898287313804</v>
       </c>
       <c r="T40">
-        <v>0.6315082887060268</v>
+        <v>0.6395225925879002</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.910393309291379</v>
+        <v>8.681921685976214</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1111161552614204</v>
+        <v>0.1107697067961136</v>
       </c>
       <c r="C41">
-        <v>320.5570025639531</v>
+        <v>319.1566590502961</v>
       </c>
       <c r="D41">
-        <v>348.1800025639531</v>
+        <v>350.0366590502962</v>
       </c>
       <c r="E41">
-        <v>-70.977</v>
+        <v>-67.72</v>
       </c>
       <c r="F41">
-        <v>127.023</v>
+        <v>130.28</v>
       </c>
       <c r="G41">
         <v>99.40000000000001</v>
@@ -4643,28 +4643,28 @@
         <v>59</v>
       </c>
       <c r="M41">
-        <v>6.795730500000001</v>
+        <v>6.969980000000001</v>
       </c>
       <c r="N41">
-        <v>52.2042695</v>
+        <v>52.03002</v>
       </c>
       <c r="O41">
-        <v>16.70536624</v>
+        <v>16.6496064</v>
       </c>
       <c r="P41">
-        <v>35.49890325999999</v>
+        <v>35.3804136</v>
       </c>
       <c r="Q41">
-        <v>47.69890325999999</v>
+        <v>47.5804136</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.158898287313804</v>
+        <v>0.1603628446601894</v>
       </c>
       <c r="T41">
-        <v>0.6395225925879002</v>
+        <v>0.6478040399325029</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.681921685976214</v>
+        <v>8.46487364382681</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1107697067961136</v>
+        <v>0.1104232583308068</v>
       </c>
       <c r="C42">
-        <v>319.1566590502961</v>
+        <v>317.7762227900619</v>
       </c>
       <c r="D42">
-        <v>350.0366590502962</v>
+        <v>351.9132227900619</v>
       </c>
       <c r="E42">
-        <v>-67.72</v>
+        <v>-64.46299999999999</v>
       </c>
       <c r="F42">
-        <v>130.28</v>
+        <v>133.537</v>
       </c>
       <c r="G42">
         <v>99.40000000000001</v>
@@ -4725,28 +4725,28 @@
         <v>59</v>
       </c>
       <c r="M42">
-        <v>6.969980000000001</v>
+        <v>7.144229500000002</v>
       </c>
       <c r="N42">
-        <v>52.03002</v>
+        <v>51.8557705</v>
       </c>
       <c r="O42">
-        <v>16.6496064</v>
+        <v>16.59384656</v>
       </c>
       <c r="P42">
-        <v>35.3804136</v>
+        <v>35.26192394</v>
       </c>
       <c r="Q42">
-        <v>47.5804136</v>
+        <v>47.46192394000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1603628446601894</v>
+        <v>0.1618770480183166</v>
       </c>
       <c r="T42">
-        <v>0.6478040399325029</v>
+        <v>0.6563662143057361</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.46487364382681</v>
+        <v>8.258413311050546</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1104232583308068</v>
+        <v>0.1100768098654999</v>
       </c>
       <c r="C43">
-        <v>317.7762227900619</v>
+        <v>316.4160156802492</v>
       </c>
       <c r="D43">
-        <v>351.9132227900619</v>
+        <v>353.8100156802493</v>
       </c>
       <c r="E43">
-        <v>-64.46299999999999</v>
+        <v>-61.20599999999999</v>
       </c>
       <c r="F43">
-        <v>133.537</v>
+        <v>136.794</v>
       </c>
       <c r="G43">
         <v>99.40000000000001</v>
@@ -4807,28 +4807,28 @@
         <v>59</v>
       </c>
       <c r="M43">
-        <v>7.144229500000002</v>
+        <v>7.318479000000002</v>
       </c>
       <c r="N43">
-        <v>51.8557705</v>
+        <v>51.681521</v>
       </c>
       <c r="O43">
-        <v>16.59384656</v>
+        <v>16.53808672</v>
       </c>
       <c r="P43">
-        <v>35.26192394</v>
+        <v>35.14343427999999</v>
       </c>
       <c r="Q43">
-        <v>47.46192394000001</v>
+        <v>47.34343428</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1618770480183166</v>
+        <v>0.1634434652853447</v>
       </c>
       <c r="T43">
-        <v>0.6563662143057361</v>
+        <v>0.6652236360711498</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.258413311050546</v>
+        <v>8.061784422692199</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1100768098654999</v>
+        <v>0.1097303614001931</v>
       </c>
       <c r="C44">
-        <v>316.4160156802491</v>
+        <v>315.0763665954942</v>
       </c>
       <c r="D44">
-        <v>353.8100156802491</v>
+        <v>355.7273665954942</v>
       </c>
       <c r="E44">
-        <v>-61.20600000000002</v>
+        <v>-57.94900000000001</v>
       </c>
       <c r="F44">
-        <v>136.794</v>
+        <v>140.051</v>
       </c>
       <c r="G44">
         <v>99.40000000000001</v>
@@ -4889,28 +4889,28 @@
         <v>59</v>
       </c>
       <c r="M44">
-        <v>7.318479000000001</v>
+        <v>7.492728500000001</v>
       </c>
       <c r="N44">
-        <v>51.681521</v>
+        <v>51.5072715</v>
       </c>
       <c r="O44">
-        <v>16.53808672</v>
+        <v>16.48232688</v>
       </c>
       <c r="P44">
-        <v>35.14343427999999</v>
+        <v>35.02494462</v>
       </c>
       <c r="Q44">
-        <v>47.34343428</v>
+        <v>47.22494462</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1634434652853447</v>
+        <v>0.1650648445617423</v>
       </c>
       <c r="T44">
-        <v>0.6652236360711498</v>
+        <v>0.6743918445651744</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.061784422692199</v>
+        <v>7.87430106402494</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1097303614001931</v>
+        <v>0.1093839129348863</v>
       </c>
       <c r="C45">
-        <v>315.0763665954942</v>
+        <v>313.7576115781656</v>
       </c>
       <c r="D45">
-        <v>355.7273665954942</v>
+        <v>357.6656115781655</v>
       </c>
       <c r="E45">
-        <v>-57.94900000000001</v>
+        <v>-54.69200000000001</v>
       </c>
       <c r="F45">
-        <v>140.051</v>
+        <v>143.308</v>
       </c>
       <c r="G45">
         <v>99.40000000000001</v>
@@ -4971,28 +4971,28 @@
         <v>59</v>
       </c>
       <c r="M45">
-        <v>7.492728500000001</v>
+        <v>7.666978000000001</v>
       </c>
       <c r="N45">
-        <v>51.5072715</v>
+        <v>51.333022</v>
       </c>
       <c r="O45">
-        <v>16.48232688</v>
+        <v>16.42656704</v>
       </c>
       <c r="P45">
-        <v>35.02494462</v>
+        <v>34.90645496</v>
       </c>
       <c r="Q45">
-        <v>47.22494462</v>
+        <v>47.10645495999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1650648445617423</v>
+        <v>0.1667441302408683</v>
       </c>
       <c r="T45">
-        <v>0.6743918445651744</v>
+        <v>0.6838874890768428</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.87430106402494</v>
+        <v>7.695339676206191</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1093839129348863</v>
+        <v>0.1092822644695794</v>
       </c>
       <c r="C46">
-        <v>313.7576115781656</v>
+        <v>311.0733094933033</v>
       </c>
       <c r="D46">
-        <v>357.6656115781655</v>
+        <v>358.2383094933033</v>
       </c>
       <c r="E46">
-        <v>-54.69200000000001</v>
+        <v>-51.435</v>
       </c>
       <c r="F46">
-        <v>143.308</v>
+        <v>146.565</v>
       </c>
       <c r="G46">
         <v>99.40000000000001</v>
@@ -5053,45 +5053,45 @@
         <v>59</v>
       </c>
       <c r="M46">
-        <v>7.666978000000001</v>
+        <v>7.958479500000002</v>
       </c>
       <c r="N46">
-        <v>51.333022</v>
+        <v>51.0415205</v>
       </c>
       <c r="O46">
-        <v>16.42656704</v>
+        <v>16.33328656</v>
       </c>
       <c r="P46">
-        <v>34.90645496</v>
+        <v>34.70823394</v>
       </c>
       <c r="Q46">
-        <v>47.10645495999999</v>
+        <v>46.90823394</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1667441302408683</v>
+        <v>0.1684844808537807</v>
       </c>
       <c r="T46">
-        <v>0.6838874890768428</v>
+        <v>0.6937284297525718</v>
       </c>
       <c r="U46">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V46">
         <v>0.32</v>
       </c>
       <c r="W46">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.695339676206191</v>
+        <v>7.413476405888836</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1092822644695794</v>
+        <v>0.1089412560042726</v>
       </c>
       <c r="C47">
-        <v>311.0733094933033</v>
+        <v>309.7510555510339</v>
       </c>
       <c r="D47">
-        <v>358.2383094933033</v>
+        <v>360.1730555510339</v>
       </c>
       <c r="E47">
-        <v>-51.435</v>
+        <v>-48.178</v>
       </c>
       <c r="F47">
-        <v>146.565</v>
+        <v>149.822</v>
       </c>
       <c r="G47">
         <v>99.40000000000001</v>
@@ -5135,28 +5135,28 @@
         <v>59</v>
       </c>
       <c r="M47">
-        <v>7.958479500000002</v>
+        <v>8.135334600000002</v>
       </c>
       <c r="N47">
-        <v>51.0415205</v>
+        <v>50.8646654</v>
       </c>
       <c r="O47">
-        <v>16.33328656</v>
+        <v>16.276692928</v>
       </c>
       <c r="P47">
-        <v>34.70823394</v>
+        <v>34.587972472</v>
       </c>
       <c r="Q47">
-        <v>46.90823394</v>
+        <v>46.78797247200001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1684844808537807</v>
+        <v>0.1702892888968011</v>
       </c>
       <c r="T47">
-        <v>0.6937284297525718</v>
+        <v>0.7039338497125873</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.413476405888836</v>
+        <v>7.252313875326036</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1089412560042726</v>
+        <v>0.1086002475389657</v>
       </c>
       <c r="C48">
-        <v>309.7510555510339</v>
+        <v>308.4498131432653</v>
       </c>
       <c r="D48">
-        <v>360.1730555510339</v>
+        <v>362.1288131432653</v>
       </c>
       <c r="E48">
-        <v>-48.178</v>
+        <v>-44.92099999999999</v>
       </c>
       <c r="F48">
-        <v>149.822</v>
+        <v>153.079</v>
       </c>
       <c r="G48">
         <v>99.40000000000001</v>
@@ -5217,28 +5217,28 @@
         <v>59</v>
       </c>
       <c r="M48">
-        <v>8.135334600000002</v>
+        <v>8.312189700000003</v>
       </c>
       <c r="N48">
-        <v>50.8646654</v>
+        <v>50.6878103</v>
       </c>
       <c r="O48">
-        <v>16.276692928</v>
+        <v>16.220099296</v>
       </c>
       <c r="P48">
-        <v>34.587972472</v>
+        <v>34.46771100399999</v>
       </c>
       <c r="Q48">
-        <v>46.78797247200001</v>
+        <v>46.667711004</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1702892888968011</v>
+        <v>0.1721622029037089</v>
       </c>
       <c r="T48">
-        <v>0.7039338497125873</v>
+        <v>0.7145243798597729</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.252313875326036</v>
+        <v>7.098009324787183</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1086002475389657</v>
+        <v>0.1082592390736589</v>
       </c>
       <c r="C49">
-        <v>308.4498131432653</v>
+        <v>307.1699264197773</v>
       </c>
       <c r="D49">
-        <v>362.1288131432653</v>
+        <v>364.1059264197773</v>
       </c>
       <c r="E49">
-        <v>-44.92099999999999</v>
+        <v>-41.66399999999999</v>
       </c>
       <c r="F49">
-        <v>153.079</v>
+        <v>156.336</v>
       </c>
       <c r="G49">
         <v>99.40000000000001</v>
@@ -5299,28 +5299,28 @@
         <v>59</v>
       </c>
       <c r="M49">
-        <v>8.312189700000003</v>
+        <v>8.489044800000002</v>
       </c>
       <c r="N49">
-        <v>50.6878103</v>
+        <v>50.5109552</v>
       </c>
       <c r="O49">
-        <v>16.220099296</v>
+        <v>16.163505664</v>
       </c>
       <c r="P49">
-        <v>34.46771100399999</v>
+        <v>34.347449536</v>
       </c>
       <c r="Q49">
-        <v>46.667711004</v>
+        <v>46.547449536</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1721622029037089</v>
+        <v>0.1741071520647287</v>
       </c>
       <c r="T49">
-        <v>0.7145243798597729</v>
+        <v>0.7255222380895427</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.098009324787183</v>
+        <v>6.950134130520785</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1082592390736589</v>
+        <v>0.1079182306083521</v>
       </c>
       <c r="C50">
-        <v>307.1699264197773</v>
+        <v>305.9117470874225</v>
       </c>
       <c r="D50">
-        <v>364.1059264197773</v>
+        <v>366.1047470874225</v>
       </c>
       <c r="E50">
-        <v>-41.66400000000002</v>
+        <v>-38.40700000000001</v>
       </c>
       <c r="F50">
-        <v>156.336</v>
+        <v>159.593</v>
       </c>
       <c r="G50">
         <v>99.40000000000001</v>
@@ -5381,28 +5381,28 @@
         <v>59</v>
       </c>
       <c r="M50">
-        <v>8.4890448</v>
+        <v>8.665899900000001</v>
       </c>
       <c r="N50">
-        <v>50.5109552</v>
+        <v>50.3341001</v>
       </c>
       <c r="O50">
-        <v>16.163505664</v>
+        <v>16.106912032</v>
       </c>
       <c r="P50">
-        <v>34.347449536</v>
+        <v>34.227188068</v>
       </c>
       <c r="Q50">
-        <v>46.547449536</v>
+        <v>46.42718806800001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1741071520647286</v>
+        <v>0.1761283737418668</v>
       </c>
       <c r="T50">
-        <v>0.7255222380895426</v>
+        <v>0.7369513848773427</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.950134130520786</v>
+        <v>6.80829465846934</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1079182306083521</v>
+        <v>0.1075772221430452</v>
       </c>
       <c r="C51">
-        <v>305.9117470874225</v>
+        <v>304.6756346187</v>
       </c>
       <c r="D51">
-        <v>366.1047470874225</v>
+        <v>368.1256346187</v>
       </c>
       <c r="E51">
-        <v>-38.40700000000001</v>
+        <v>-35.15000000000001</v>
       </c>
       <c r="F51">
-        <v>159.593</v>
+        <v>162.85</v>
       </c>
       <c r="G51">
         <v>99.40000000000001</v>
@@ -5463,28 +5463,28 @@
         <v>59</v>
       </c>
       <c r="M51">
-        <v>8.665899900000001</v>
+        <v>8.842755000000002</v>
       </c>
       <c r="N51">
-        <v>50.3341001</v>
+        <v>50.157245</v>
       </c>
       <c r="O51">
-        <v>16.106912032</v>
+        <v>16.0503184</v>
       </c>
       <c r="P51">
-        <v>34.227188068</v>
+        <v>34.10692659999999</v>
       </c>
       <c r="Q51">
-        <v>46.42718806800001</v>
+        <v>46.3069266</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1761283737418668</v>
+        <v>0.1782304442860904</v>
       </c>
       <c r="T51">
-        <v>0.7369513848773427</v>
+        <v>0.7488376975366546</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.80829465846934</v>
+        <v>6.672128765299953</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1075772221430452</v>
+        <v>0.1072362136777384</v>
       </c>
       <c r="C52">
-        <v>304.6756346187</v>
+        <v>303.4619564672747</v>
       </c>
       <c r="D52">
-        <v>368.1256346187</v>
+        <v>370.1689564672747</v>
       </c>
       <c r="E52">
-        <v>-35.15000000000001</v>
+        <v>-31.893</v>
       </c>
       <c r="F52">
-        <v>162.85</v>
+        <v>166.107</v>
       </c>
       <c r="G52">
         <v>99.40000000000001</v>
@@ -5545,28 +5545,28 @@
         <v>59</v>
       </c>
       <c r="M52">
-        <v>8.842755000000002</v>
+        <v>9.019610100000001</v>
       </c>
       <c r="N52">
-        <v>50.157245</v>
+        <v>49.9803899</v>
       </c>
       <c r="O52">
-        <v>16.0503184</v>
+        <v>15.993724768</v>
       </c>
       <c r="P52">
-        <v>34.10692659999999</v>
+        <v>33.986665132</v>
       </c>
       <c r="Q52">
-        <v>46.3069266</v>
+        <v>46.186665132</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1782304442860904</v>
+        <v>0.1804183136280375</v>
       </c>
       <c r="T52">
-        <v>0.7488376975366546</v>
+        <v>0.7612091658147141</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.672128765299953</v>
+        <v>6.541302711078386</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1072362136777384</v>
+        <v>0.1068952052124315</v>
       </c>
       <c r="C53">
-        <v>303.4619564672747</v>
+        <v>302.271088290717</v>
       </c>
       <c r="D53">
-        <v>370.1689564672747</v>
+        <v>372.235088290717</v>
       </c>
       <c r="E53">
-        <v>-31.893</v>
+        <v>-28.636</v>
       </c>
       <c r="F53">
-        <v>166.107</v>
+        <v>169.364</v>
       </c>
       <c r="G53">
         <v>99.40000000000001</v>
@@ -5627,28 +5627,28 @@
         <v>59</v>
       </c>
       <c r="M53">
-        <v>9.019610100000001</v>
+        <v>9.196465200000002</v>
       </c>
       <c r="N53">
-        <v>49.9803899</v>
+        <v>49.80353479999999</v>
       </c>
       <c r="O53">
-        <v>15.993724768</v>
+        <v>15.937131136</v>
       </c>
       <c r="P53">
-        <v>33.986665132</v>
+        <v>33.866403664</v>
       </c>
       <c r="Q53">
-        <v>46.186665132</v>
+        <v>46.06640366399999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1804183136280375</v>
+        <v>0.1826973441925657</v>
       </c>
       <c r="T53">
-        <v>0.7612091658147141</v>
+        <v>0.7740961119376927</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.541302711078386</v>
+        <v>6.415508428173031</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1068952052124315</v>
+        <v>0.1065541967471247</v>
       </c>
       <c r="C54">
-        <v>302.271088290717</v>
+        <v>301.1034141807408</v>
       </c>
       <c r="D54">
-        <v>372.235088290717</v>
+        <v>374.3244141807408</v>
       </c>
       <c r="E54">
-        <v>-28.636</v>
+        <v>-25.37899999999999</v>
       </c>
       <c r="F54">
-        <v>169.364</v>
+        <v>172.621</v>
       </c>
       <c r="G54">
         <v>99.40000000000001</v>
@@ -5709,28 +5709,28 @@
         <v>59</v>
       </c>
       <c r="M54">
-        <v>9.196465200000002</v>
+        <v>9.373320300000001</v>
       </c>
       <c r="N54">
-        <v>49.80353479999999</v>
+        <v>49.6266797</v>
       </c>
       <c r="O54">
-        <v>15.937131136</v>
+        <v>15.880537504</v>
       </c>
       <c r="P54">
-        <v>33.866403664</v>
+        <v>33.74614219599999</v>
       </c>
       <c r="Q54">
-        <v>46.06640366399999</v>
+        <v>45.946142196</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1826973441925657</v>
+        <v>0.1850733547811164</v>
       </c>
       <c r="T54">
-        <v>0.7740961119376927</v>
+        <v>0.7875314387467555</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.415508428173031</v>
+        <v>6.294461099339578</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1065541967471247</v>
+        <v>0.1062131882818179</v>
       </c>
       <c r="C55">
-        <v>301.1034141807408</v>
+        <v>299.9593269012415</v>
       </c>
       <c r="D55">
-        <v>374.3244141807408</v>
+        <v>376.4373269012415</v>
       </c>
       <c r="E55">
-        <v>-25.37899999999999</v>
+        <v>-22.12199999999999</v>
       </c>
       <c r="F55">
-        <v>172.621</v>
+        <v>175.878</v>
       </c>
       <c r="G55">
         <v>99.40000000000001</v>
@@ -5791,28 +5791,28 @@
         <v>59</v>
       </c>
       <c r="M55">
-        <v>9.373320300000001</v>
+        <v>9.550175400000002</v>
       </c>
       <c r="N55">
-        <v>49.6266797</v>
+        <v>49.4498246</v>
       </c>
       <c r="O55">
-        <v>15.880537504</v>
+        <v>15.823943872</v>
       </c>
       <c r="P55">
-        <v>33.74614219599999</v>
+        <v>33.625880728</v>
       </c>
       <c r="Q55">
-        <v>45.946142196</v>
+        <v>45.825880728</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1850733547811164</v>
+        <v>0.1875526701778649</v>
       </c>
       <c r="T55">
-        <v>0.7875314387467555</v>
+        <v>0.8015509101996904</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.294461099339578</v>
+        <v>6.177897004907364</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1062131882818179</v>
+        <v>0.106246179816511</v>
       </c>
       <c r="C56">
-        <v>299.9593269012415</v>
+        <v>296.4968673475035</v>
       </c>
       <c r="D56">
-        <v>376.4373269012415</v>
+        <v>376.2318673475035</v>
       </c>
       <c r="E56">
-        <v>-22.12199999999999</v>
+        <v>-18.86499999999998</v>
       </c>
       <c r="F56">
-        <v>175.878</v>
+        <v>179.135</v>
       </c>
       <c r="G56">
         <v>99.40000000000001</v>
@@ -5873,45 +5873,45 @@
         <v>59</v>
       </c>
       <c r="M56">
-        <v>9.550175400000002</v>
+        <v>9.906165500000004</v>
       </c>
       <c r="N56">
-        <v>49.4498246</v>
+        <v>49.0938345</v>
       </c>
       <c r="O56">
-        <v>15.823943872</v>
+        <v>15.71002704</v>
       </c>
       <c r="P56">
-        <v>33.625880728</v>
+        <v>33.38380746</v>
       </c>
       <c r="Q56">
-        <v>45.825880728</v>
+        <v>45.58380746</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1875526701778649</v>
+        <v>0.1901421773700245</v>
       </c>
       <c r="T56">
-        <v>0.8015509101996904</v>
+        <v>0.816193469272756</v>
       </c>
       <c r="U56">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.32</v>
       </c>
       <c r="W56">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>6.177897004907364</v>
+        <v>5.955886765671337</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.106246179816511</v>
+        <v>0.1059119713512042</v>
       </c>
       <c r="C57">
-        <v>296.4968673475035</v>
+        <v>295.3316283089118</v>
       </c>
       <c r="D57">
-        <v>376.2318673475035</v>
+        <v>378.3236283089119</v>
       </c>
       <c r="E57">
-        <v>-18.86499999999998</v>
+        <v>-15.60799999999998</v>
       </c>
       <c r="F57">
-        <v>179.135</v>
+        <v>182.3920000000001</v>
       </c>
       <c r="G57">
         <v>99.40000000000001</v>
@@ -5955,28 +5955,28 @@
         <v>59</v>
       </c>
       <c r="M57">
-        <v>9.906165500000004</v>
+        <v>10.0862776</v>
       </c>
       <c r="N57">
-        <v>49.0938345</v>
+        <v>48.9137224</v>
       </c>
       <c r="O57">
-        <v>15.71002704</v>
+        <v>15.652391168</v>
       </c>
       <c r="P57">
-        <v>33.38380746</v>
+        <v>33.261331232</v>
       </c>
       <c r="Q57">
-        <v>45.58380746</v>
+        <v>45.46133123199999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1901421773700245</v>
+        <v>0.192849389434555</v>
       </c>
       <c r="T57">
-        <v>0.816193469272756</v>
+        <v>0.8315015992127789</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.955886765671337</v>
+        <v>5.849531644855777</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1059119713512042</v>
+        <v>0.1055777628858974</v>
       </c>
       <c r="C58">
-        <v>295.3316283089118</v>
+        <v>294.18977871104</v>
       </c>
       <c r="D58">
-        <v>378.3236283089119</v>
+        <v>380.43877871104</v>
       </c>
       <c r="E58">
-        <v>-15.60799999999998</v>
+        <v>-12.35099999999997</v>
       </c>
       <c r="F58">
-        <v>182.3920000000001</v>
+        <v>185.6490000000001</v>
       </c>
       <c r="G58">
         <v>99.40000000000001</v>
@@ -6037,28 +6037,28 @@
         <v>59</v>
       </c>
       <c r="M58">
-        <v>10.0862776</v>
+        <v>10.2663897</v>
       </c>
       <c r="N58">
-        <v>48.9137224</v>
+        <v>48.7336103</v>
       </c>
       <c r="O58">
-        <v>15.652391168</v>
+        <v>15.594755296</v>
       </c>
       <c r="P58">
-        <v>33.261331232</v>
+        <v>33.13885500399999</v>
       </c>
       <c r="Q58">
-        <v>45.46133123199999</v>
+        <v>45.338855004</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.192849389434555</v>
+        <v>0.1956825183392962</v>
       </c>
       <c r="T58">
-        <v>0.8315015992127789</v>
+        <v>0.8475217351965241</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.849531644855777</v>
+        <v>5.746908282665325</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1055777628858974</v>
+        <v>0.1052435544205905</v>
       </c>
       <c r="C59">
-        <v>294.18977871104</v>
+        <v>293.0717130600295</v>
       </c>
       <c r="D59">
-        <v>380.43877871104</v>
+        <v>382.5777130600296</v>
       </c>
       <c r="E59">
-        <v>-12.35099999999997</v>
+        <v>-9.093999999999966</v>
       </c>
       <c r="F59">
-        <v>185.6490000000001</v>
+        <v>188.9060000000001</v>
       </c>
       <c r="G59">
         <v>99.40000000000001</v>
@@ -6119,28 +6119,28 @@
         <v>59</v>
       </c>
       <c r="M59">
-        <v>10.2663897</v>
+        <v>10.4465018</v>
       </c>
       <c r="N59">
-        <v>48.7336103</v>
+        <v>48.55349819999999</v>
       </c>
       <c r="O59">
-        <v>15.594755296</v>
+        <v>15.537119424</v>
       </c>
       <c r="P59">
-        <v>33.13885500399999</v>
+        <v>33.016378776</v>
       </c>
       <c r="Q59">
-        <v>45.338855004</v>
+        <v>45.216378776</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1956825183392962</v>
+        <v>0.1986505581442631</v>
       </c>
       <c r="T59">
-        <v>0.8475217351965241</v>
+        <v>0.8643047347985426</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.746908282665325</v>
+        <v>5.647823657102129</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1052435544205905</v>
+        <v>0.1049093459552837</v>
       </c>
       <c r="C60">
-        <v>293.0717130600296</v>
+        <v>291.9778347842847</v>
       </c>
       <c r="D60">
-        <v>382.5777130600296</v>
+        <v>384.7408347842847</v>
       </c>
       <c r="E60">
-        <v>-9.094000000000023</v>
+        <v>-5.837000000000018</v>
       </c>
       <c r="F60">
-        <v>188.906</v>
+        <v>192.163</v>
       </c>
       <c r="G60">
         <v>99.40000000000001</v>
@@ -6201,28 +6201,28 @@
         <v>59</v>
       </c>
       <c r="M60">
-        <v>10.4465018</v>
+        <v>10.6266139</v>
       </c>
       <c r="N60">
-        <v>48.5534982</v>
+        <v>48.3733861</v>
       </c>
       <c r="O60">
-        <v>15.537119424</v>
+        <v>15.479483552</v>
       </c>
       <c r="P60">
-        <v>33.016378776</v>
+        <v>32.893902548</v>
       </c>
       <c r="Q60">
-        <v>45.216378776</v>
+        <v>45.093902548</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1986505581442631</v>
+        <v>0.2017633803787406</v>
       </c>
       <c r="T60">
-        <v>0.8643047347985424</v>
+        <v>0.8819064173079765</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.647823657102132</v>
+        <v>5.552097832405485</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1049093459552837</v>
+        <v>0.1045751374899768</v>
       </c>
       <c r="C61">
-        <v>291.9778347842847</v>
+        <v>290.9085564881439</v>
       </c>
       <c r="D61">
-        <v>384.7408347842847</v>
+        <v>386.928556488144</v>
       </c>
       <c r="E61">
-        <v>-5.837000000000018</v>
+        <v>-2.580000000000013</v>
       </c>
       <c r="F61">
-        <v>192.163</v>
+        <v>195.42</v>
       </c>
       <c r="G61">
         <v>99.40000000000001</v>
@@ -6283,28 +6283,28 @@
         <v>59</v>
       </c>
       <c r="M61">
-        <v>10.6266139</v>
+        <v>10.806726</v>
       </c>
       <c r="N61">
-        <v>48.3733861</v>
+        <v>48.193274</v>
       </c>
       <c r="O61">
-        <v>15.479483552</v>
+        <v>15.42184768</v>
       </c>
       <c r="P61">
-        <v>32.893902548</v>
+        <v>32.77142632</v>
       </c>
       <c r="Q61">
-        <v>45.093902548</v>
+        <v>44.97142632000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2017633803787406</v>
+        <v>0.205031843724942</v>
       </c>
       <c r="T61">
-        <v>0.8819064173079765</v>
+        <v>0.9003881839428822</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.552097832405485</v>
+        <v>5.459562868532061</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1045751374899768</v>
+        <v>0.10424092902467</v>
       </c>
       <c r="C62">
-        <v>290.9085564881439</v>
+        <v>289.8643002142524</v>
       </c>
       <c r="D62">
-        <v>386.928556488144</v>
+        <v>389.1413002142524</v>
       </c>
       <c r="E62">
-        <v>-2.580000000000013</v>
+        <v>0.6769999999999925</v>
       </c>
       <c r="F62">
-        <v>195.42</v>
+        <v>198.677</v>
       </c>
       <c r="G62">
         <v>99.40000000000001</v>
@@ -6365,28 +6365,28 @@
         <v>59</v>
       </c>
       <c r="M62">
-        <v>10.806726</v>
+        <v>10.9868381</v>
       </c>
       <c r="N62">
-        <v>48.193274</v>
+        <v>48.0131619</v>
       </c>
       <c r="O62">
-        <v>15.42184768</v>
+        <v>15.364211808</v>
       </c>
       <c r="P62">
-        <v>32.77142632</v>
+        <v>32.648950092</v>
       </c>
       <c r="Q62">
-        <v>44.97142632000001</v>
+        <v>44.848950092</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.205031843724942</v>
+        <v>0.2084679205760769</v>
       </c>
       <c r="T62">
-        <v>0.9003881839428822</v>
+        <v>0.9198177334821424</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.459562868532061</v>
+        <v>5.370061837900387</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.10424092902467</v>
+        <v>0.1039067205593631</v>
       </c>
       <c r="C63">
-        <v>289.8643002142524</v>
+        <v>288.8454977149916</v>
       </c>
       <c r="D63">
-        <v>389.1413002142524</v>
+        <v>391.3794977149917</v>
       </c>
       <c r="E63">
-        <v>0.6769999999999925</v>
+        <v>3.933999999999997</v>
       </c>
       <c r="F63">
-        <v>198.677</v>
+        <v>201.934</v>
       </c>
       <c r="G63">
         <v>99.40000000000001</v>
@@ -6447,28 +6447,28 @@
         <v>59</v>
       </c>
       <c r="M63">
-        <v>10.9868381</v>
+        <v>11.1669502</v>
       </c>
       <c r="N63">
-        <v>48.0131619</v>
+        <v>47.8330498</v>
       </c>
       <c r="O63">
-        <v>15.364211808</v>
+        <v>15.306575936</v>
       </c>
       <c r="P63">
-        <v>32.648950092</v>
+        <v>32.526473864</v>
       </c>
       <c r="Q63">
-        <v>44.848950092</v>
+        <v>44.726473864</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2084679205760769</v>
+        <v>0.2120848435772714</v>
       </c>
       <c r="T63">
-        <v>0.9198177334821424</v>
+        <v>0.9402698908918896</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.370061837900387</v>
+        <v>5.28344793728909</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1039067205593631</v>
+        <v>0.1035725120940563</v>
       </c>
       <c r="C64">
-        <v>288.8454977149916</v>
+        <v>287.8525907333276</v>
       </c>
       <c r="D64">
-        <v>391.3794977149917</v>
+        <v>393.6435907333276</v>
       </c>
       <c r="E64">
-        <v>3.933999999999997</v>
+        <v>7.191000000000003</v>
       </c>
       <c r="F64">
-        <v>201.934</v>
+        <v>205.191</v>
       </c>
       <c r="G64">
         <v>99.40000000000001</v>
@@ -6529,28 +6529,28 @@
         <v>59</v>
       </c>
       <c r="M64">
-        <v>11.1669502</v>
+        <v>11.3470623</v>
       </c>
       <c r="N64">
-        <v>47.8330498</v>
+        <v>47.6529377</v>
       </c>
       <c r="O64">
-        <v>15.306575936</v>
+        <v>15.248940064</v>
       </c>
       <c r="P64">
-        <v>32.526473864</v>
+        <v>32.403997636</v>
       </c>
       <c r="Q64">
-        <v>44.726473864</v>
+        <v>44.603997636</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2120848435772714</v>
+        <v>0.2158972759298819</v>
       </c>
       <c r="T64">
-        <v>0.9402698908918896</v>
+        <v>0.9618275703237856</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.28344793728909</v>
+        <v>5.199583684316247</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1035725120940563</v>
+        <v>0.1032383036287495</v>
       </c>
       <c r="C65">
-        <v>287.8525907333276</v>
+        <v>286.8860312934665</v>
       </c>
       <c r="D65">
-        <v>393.6435907333276</v>
+        <v>395.9340312934665</v>
       </c>
       <c r="E65">
-        <v>7.191000000000003</v>
+        <v>10.44800000000001</v>
       </c>
       <c r="F65">
-        <v>205.191</v>
+        <v>208.448</v>
       </c>
       <c r="G65">
         <v>99.40000000000001</v>
@@ -6611,28 +6611,28 @@
         <v>59</v>
       </c>
       <c r="M65">
-        <v>11.3470623</v>
+        <v>11.5271744</v>
       </c>
       <c r="N65">
-        <v>47.6529377</v>
+        <v>47.4728256</v>
       </c>
       <c r="O65">
-        <v>15.248940064</v>
+        <v>15.191304192</v>
       </c>
       <c r="P65">
-        <v>32.403997636</v>
+        <v>32.281521408</v>
       </c>
       <c r="Q65">
-        <v>44.603997636</v>
+        <v>44.48152140800001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2158972759298819</v>
+        <v>0.2199215100798596</v>
       </c>
       <c r="T65">
-        <v>0.9618275703237856</v>
+        <v>0.9845828986130089</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.199583684316247</v>
+        <v>5.118340189248806</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1032383036287495</v>
+        <v>0.1029040951634426</v>
       </c>
       <c r="C66">
-        <v>286.8860312934665</v>
+        <v>285.9462820017143</v>
       </c>
       <c r="D66">
-        <v>395.9340312934665</v>
+        <v>398.2512820017143</v>
       </c>
       <c r="E66">
-        <v>10.44800000000001</v>
+        <v>13.70500000000001</v>
       </c>
       <c r="F66">
-        <v>208.448</v>
+        <v>211.705</v>
       </c>
       <c r="G66">
         <v>99.40000000000001</v>
@@ -6693,28 +6693,28 @@
         <v>59</v>
       </c>
       <c r="M66">
-        <v>11.5271744</v>
+        <v>11.7072865</v>
       </c>
       <c r="N66">
-        <v>47.4728256</v>
+        <v>47.2927135</v>
       </c>
       <c r="O66">
-        <v>15.191304192</v>
+        <v>15.13366832</v>
       </c>
       <c r="P66">
-        <v>32.281521408</v>
+        <v>32.15904518</v>
       </c>
       <c r="Q66">
-        <v>44.48152140800001</v>
+        <v>44.35904518</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2199215100798596</v>
+        <v>0.224175700466979</v>
       </c>
       <c r="T66">
-        <v>0.9845828986130089</v>
+        <v>1.008638531375902</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.118340189248806</v>
+        <v>5.039596494029594</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1029040951634426</v>
+        <v>0.1025698866981358</v>
       </c>
       <c r="C67">
-        <v>285.9462820017143</v>
+        <v>285.0338163579656</v>
       </c>
       <c r="D67">
-        <v>398.2512820017143</v>
+        <v>400.5958163579656</v>
       </c>
       <c r="E67">
-        <v>13.70500000000001</v>
+        <v>16.96200000000002</v>
       </c>
       <c r="F67">
-        <v>211.705</v>
+        <v>214.962</v>
       </c>
       <c r="G67">
         <v>99.40000000000001</v>
@@ -6775,28 +6775,28 @@
         <v>59</v>
       </c>
       <c r="M67">
-        <v>11.7072865</v>
+        <v>11.8873986</v>
       </c>
       <c r="N67">
-        <v>47.2927135</v>
+        <v>47.1126014</v>
       </c>
       <c r="O67">
-        <v>15.13366832</v>
+        <v>15.076032448</v>
       </c>
       <c r="P67">
-        <v>32.15904518</v>
+        <v>32.036568952</v>
       </c>
       <c r="Q67">
-        <v>44.35904518</v>
+        <v>44.236568952</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.224175700466979</v>
+        <v>0.2286801373474582</v>
       </c>
       <c r="T67">
-        <v>1.008638531375902</v>
+        <v>1.034109201360142</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.039596494029594</v>
+        <v>4.963238971392781</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1025698866981358</v>
+        <v>0.102235678232829</v>
       </c>
       <c r="C68">
-        <v>285.0338163579656</v>
+        <v>284.1491190782589</v>
       </c>
       <c r="D68">
-        <v>400.5958163579656</v>
+        <v>402.9681190782589</v>
       </c>
       <c r="E68">
-        <v>16.96200000000002</v>
+        <v>20.21900000000002</v>
       </c>
       <c r="F68">
-        <v>214.962</v>
+        <v>218.2190000000001</v>
       </c>
       <c r="G68">
         <v>99.40000000000001</v>
@@ -6857,28 +6857,28 @@
         <v>59</v>
       </c>
       <c r="M68">
-        <v>11.8873986</v>
+        <v>12.0675107</v>
       </c>
       <c r="N68">
-        <v>47.1126014</v>
+        <v>46.9324893</v>
       </c>
       <c r="O68">
-        <v>15.076032448</v>
+        <v>15.018396576</v>
       </c>
       <c r="P68">
-        <v>32.036568952</v>
+        <v>31.914092724</v>
       </c>
       <c r="Q68">
-        <v>44.236568952</v>
+        <v>44.114092724</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2286801373474582</v>
+        <v>0.233457570402512</v>
       </c>
       <c r="T68">
-        <v>1.034109201360142</v>
+        <v>1.061123548313124</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.963238971392781</v>
+        <v>4.889160777789904</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.102235678232829</v>
+        <v>0.1019014697675221</v>
       </c>
       <c r="C69">
-        <v>284.1491190782589</v>
+        <v>283.2926864288615</v>
       </c>
       <c r="D69">
-        <v>402.9681190782589</v>
+        <v>405.3686864288615</v>
       </c>
       <c r="E69">
-        <v>20.21900000000002</v>
+        <v>23.47600000000003</v>
       </c>
       <c r="F69">
-        <v>218.2190000000001</v>
+        <v>221.4760000000001</v>
       </c>
       <c r="G69">
         <v>99.40000000000001</v>
@@ -6939,28 +6939,28 @@
         <v>59</v>
       </c>
       <c r="M69">
-        <v>12.0675107</v>
+        <v>12.2476228</v>
       </c>
       <c r="N69">
-        <v>46.9324893</v>
+        <v>46.7523772</v>
       </c>
       <c r="O69">
-        <v>15.018396576</v>
+        <v>14.960760704</v>
       </c>
       <c r="P69">
-        <v>31.914092724</v>
+        <v>31.791616496</v>
       </c>
       <c r="Q69">
-        <v>44.114092724</v>
+        <v>43.99161649599999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.233457570402512</v>
+        <v>0.2385335930235066</v>
       </c>
       <c r="T69">
-        <v>1.061123548313124</v>
+        <v>1.089826291950667</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.889160777789904</v>
+        <v>4.817261354587111</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1019014697675221</v>
+        <v>0.1015672613022153</v>
       </c>
       <c r="C70">
-        <v>283.2926864288615</v>
+        <v>282.4650265723672</v>
       </c>
       <c r="D70">
-        <v>405.3686864288615</v>
+        <v>407.7980265723672</v>
       </c>
       <c r="E70">
-        <v>23.47600000000003</v>
+        <v>26.73300000000003</v>
       </c>
       <c r="F70">
-        <v>221.4760000000001</v>
+        <v>224.7330000000001</v>
       </c>
       <c r="G70">
         <v>99.40000000000001</v>
@@ -7021,28 +7021,28 @@
         <v>59</v>
       </c>
       <c r="M70">
-        <v>12.2476228</v>
+        <v>12.4277349</v>
       </c>
       <c r="N70">
-        <v>46.7523772</v>
+        <v>46.5722651</v>
       </c>
       <c r="O70">
-        <v>14.960760704</v>
+        <v>14.903124832</v>
       </c>
       <c r="P70">
-        <v>31.791616496</v>
+        <v>31.669140268</v>
       </c>
       <c r="Q70">
-        <v>43.99161649599999</v>
+        <v>43.869140268</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2385335930235066</v>
+        <v>0.243937100974888</v>
       </c>
       <c r="T70">
-        <v>1.089826291950667</v>
+        <v>1.12038082550031</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.817261354587111</v>
+        <v>4.747445972636573</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1015672613022153</v>
+        <v>0.1012330528369084</v>
       </c>
       <c r="C71">
-        <v>282.4650265723672</v>
+        <v>281.6666599263136</v>
       </c>
       <c r="D71">
-        <v>407.7980265723672</v>
+        <v>410.2566599263137</v>
       </c>
       <c r="E71">
-        <v>26.73300000000003</v>
+        <v>29.99000000000004</v>
       </c>
       <c r="F71">
-        <v>224.7330000000001</v>
+        <v>227.9900000000001</v>
       </c>
       <c r="G71">
         <v>99.40000000000001</v>
@@ -7103,28 +7103,28 @@
         <v>59</v>
       </c>
       <c r="M71">
-        <v>12.4277349</v>
+        <v>12.607847</v>
       </c>
       <c r="N71">
-        <v>46.5722651</v>
+        <v>46.39215299999999</v>
       </c>
       <c r="O71">
-        <v>14.903124832</v>
+        <v>14.84548896</v>
       </c>
       <c r="P71">
-        <v>31.669140268</v>
+        <v>31.54666404</v>
       </c>
       <c r="Q71">
-        <v>43.869140268</v>
+        <v>43.74666404</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.243937100974888</v>
+        <v>0.2497008427896948</v>
       </c>
       <c r="T71">
-        <v>1.12038082550031</v>
+        <v>1.152972327953262</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.747445972636573</v>
+        <v>4.679625315884621</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1012330528369084</v>
+        <v>0.1008988443716016</v>
       </c>
       <c r="C72">
-        <v>281.6666599263136</v>
+        <v>280.8981195348523</v>
       </c>
       <c r="D72">
-        <v>410.2566599263137</v>
+        <v>412.7451195348524</v>
       </c>
       <c r="E72">
-        <v>29.99000000000004</v>
+        <v>33.24700000000004</v>
       </c>
       <c r="F72">
-        <v>227.9900000000001</v>
+        <v>231.2470000000001</v>
       </c>
       <c r="G72">
         <v>99.40000000000001</v>
@@ -7185,28 +7185,28 @@
         <v>59</v>
       </c>
       <c r="M72">
-        <v>12.607847</v>
+        <v>12.7879591</v>
       </c>
       <c r="N72">
-        <v>46.39215299999999</v>
+        <v>46.2120409</v>
       </c>
       <c r="O72">
-        <v>14.84548896</v>
+        <v>14.787853088</v>
       </c>
       <c r="P72">
-        <v>31.54666404</v>
+        <v>31.424187812</v>
       </c>
       <c r="Q72">
-        <v>43.74666404</v>
+        <v>43.624187812</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2497008427896948</v>
+        <v>0.2558620840400055</v>
       </c>
       <c r="T72">
-        <v>1.152972327953262</v>
+        <v>1.187811520230556</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.679625315884621</v>
+        <v>4.613715100167937</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1008988443716016</v>
+        <v>0.1005646359062948</v>
       </c>
       <c r="C73">
-        <v>280.8981195348522</v>
+        <v>280.1599514540246</v>
       </c>
       <c r="D73">
-        <v>412.7451195348523</v>
+        <v>415.2639514540247</v>
       </c>
       <c r="E73">
-        <v>33.24699999999999</v>
+        <v>36.50399999999999</v>
       </c>
       <c r="F73">
-        <v>231.247</v>
+        <v>234.504</v>
       </c>
       <c r="G73">
         <v>99.40000000000001</v>
@@ -7267,28 +7267,28 @@
         <v>59</v>
       </c>
       <c r="M73">
-        <v>12.7879591</v>
+        <v>12.9680712</v>
       </c>
       <c r="N73">
-        <v>46.2120409</v>
+        <v>46.0319288</v>
       </c>
       <c r="O73">
-        <v>14.787853088</v>
+        <v>14.730217216</v>
       </c>
       <c r="P73">
-        <v>31.424187812</v>
+        <v>31.301711584</v>
       </c>
       <c r="Q73">
-        <v>43.624187812</v>
+        <v>43.50171158400001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2558620840400055</v>
+        <v>0.2624634139510527</v>
       </c>
       <c r="T73">
-        <v>1.187811520230555</v>
+        <v>1.225139226241942</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.613715100167938</v>
+        <v>4.549635723776717</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1005646359062948</v>
+        <v>0.1014714274409879</v>
       </c>
       <c r="C74">
-        <v>280.1599514540246</v>
+        <v>270.1390179040743</v>
       </c>
       <c r="D74">
-        <v>415.2639514540247</v>
+        <v>408.5000179040742</v>
       </c>
       <c r="E74">
-        <v>36.50399999999999</v>
+        <v>39.761</v>
       </c>
       <c r="F74">
-        <v>234.504</v>
+        <v>237.761</v>
       </c>
       <c r="G74">
         <v>99.40000000000001</v>
@@ -7349,45 +7349,45 @@
         <v>59</v>
       </c>
       <c r="M74">
-        <v>12.9680712</v>
+        <v>13.7425858</v>
       </c>
       <c r="N74">
-        <v>46.0319288</v>
+        <v>45.2574142</v>
       </c>
       <c r="O74">
-        <v>14.730217216</v>
+        <v>14.482372544</v>
       </c>
       <c r="P74">
-        <v>31.301711584</v>
+        <v>30.775041656</v>
       </c>
       <c r="Q74">
-        <v>43.50171158400001</v>
+        <v>42.975041656</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2624634139510527</v>
+        <v>0.2695537312629182</v>
       </c>
       <c r="T74">
-        <v>1.225139226241942</v>
+        <v>1.26523194751343</v>
       </c>
       <c r="U74">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V74">
         <v>0.32</v>
       </c>
       <c r="W74">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>4.549635723776717</v>
+        <v>4.293224059769013</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1014714274409879</v>
+        <v>0.1011542189756811</v>
       </c>
       <c r="C75">
-        <v>270.1390179040743</v>
+        <v>269.2229354737735</v>
       </c>
       <c r="D75">
-        <v>408.5000179040742</v>
+        <v>410.8409354737736</v>
       </c>
       <c r="E75">
-        <v>39.761</v>
+        <v>43.018</v>
       </c>
       <c r="F75">
-        <v>237.761</v>
+        <v>241.018</v>
       </c>
       <c r="G75">
         <v>99.40000000000001</v>
@@ -7431,28 +7431,28 @@
         <v>59</v>
       </c>
       <c r="M75">
-        <v>13.7425858</v>
+        <v>13.9308404</v>
       </c>
       <c r="N75">
-        <v>45.2574142</v>
+        <v>45.0691596</v>
       </c>
       <c r="O75">
-        <v>14.482372544</v>
+        <v>14.422131072</v>
       </c>
       <c r="P75">
-        <v>30.775041656</v>
+        <v>30.647028528</v>
       </c>
       <c r="Q75">
-        <v>42.975041656</v>
+        <v>42.847028528</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2695537312629182</v>
+        <v>0.2771894575987734</v>
       </c>
       <c r="T75">
-        <v>1.26523194751343</v>
+        <v>1.308408724267342</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.293224059769013</v>
+        <v>4.235207518420783</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1011542189756811</v>
+        <v>0.1008370105103742</v>
       </c>
       <c r="C76">
-        <v>269.2229354737735</v>
+        <v>268.3338370261716</v>
       </c>
       <c r="D76">
-        <v>410.8409354737736</v>
+        <v>413.2088370261716</v>
       </c>
       <c r="E76">
-        <v>43.018</v>
+        <v>46.27500000000001</v>
       </c>
       <c r="F76">
-        <v>241.018</v>
+        <v>244.275</v>
       </c>
       <c r="G76">
         <v>99.40000000000001</v>
@@ -7513,28 +7513,28 @@
         <v>59</v>
       </c>
       <c r="M76">
-        <v>13.9308404</v>
+        <v>14.119095</v>
       </c>
       <c r="N76">
-        <v>45.0691596</v>
+        <v>44.880905</v>
       </c>
       <c r="O76">
-        <v>14.422131072</v>
+        <v>14.3618896</v>
       </c>
       <c r="P76">
-        <v>30.647028528</v>
+        <v>30.5190154</v>
       </c>
       <c r="Q76">
-        <v>42.847028528</v>
+        <v>42.7190154</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2771894575987734</v>
+        <v>0.285436042041497</v>
       </c>
       <c r="T76">
-        <v>1.308408724267342</v>
+        <v>1.355039643161566</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.235207518420783</v>
+        <v>4.178738084841839</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1008370105103742</v>
+        <v>0.1005198020450674</v>
       </c>
       <c r="C77">
-        <v>268.3338370261716</v>
+        <v>267.4721918364163</v>
       </c>
       <c r="D77">
-        <v>413.2088370261716</v>
+        <v>415.6041918364164</v>
       </c>
       <c r="E77">
-        <v>46.27500000000001</v>
+        <v>49.53200000000001</v>
       </c>
       <c r="F77">
-        <v>244.275</v>
+        <v>247.532</v>
       </c>
       <c r="G77">
         <v>99.40000000000001</v>
@@ -7595,28 +7595,28 @@
         <v>59</v>
       </c>
       <c r="M77">
-        <v>14.119095</v>
+        <v>14.3073496</v>
       </c>
       <c r="N77">
-        <v>44.880905</v>
+        <v>44.6926504</v>
       </c>
       <c r="O77">
-        <v>14.3618896</v>
+        <v>14.301648128</v>
       </c>
       <c r="P77">
-        <v>30.5190154</v>
+        <v>30.391002272</v>
       </c>
       <c r="Q77">
-        <v>42.7190154</v>
+        <v>42.591002272</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.285436042041497</v>
+        <v>0.2943698418544475</v>
       </c>
       <c r="T77">
-        <v>1.355039643161566</v>
+        <v>1.405556471963642</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.178738084841839</v>
+        <v>4.123754688988657</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1005198020450674</v>
+        <v>0.1002025935797606</v>
       </c>
       <c r="C78">
-        <v>267.4721918364163</v>
+        <v>266.6384801245793</v>
       </c>
       <c r="D78">
-        <v>415.6041918364164</v>
+        <v>418.0274801245793</v>
       </c>
       <c r="E78">
-        <v>49.53200000000001</v>
+        <v>52.78900000000002</v>
       </c>
       <c r="F78">
-        <v>247.532</v>
+        <v>250.789</v>
       </c>
       <c r="G78">
         <v>99.40000000000001</v>
@@ -7677,28 +7677,28 @@
         <v>59</v>
       </c>
       <c r="M78">
-        <v>14.3073496</v>
+        <v>14.4956042</v>
       </c>
       <c r="N78">
-        <v>44.6926504</v>
+        <v>44.5043958</v>
       </c>
       <c r="O78">
-        <v>14.301648128</v>
+        <v>14.241406656</v>
       </c>
       <c r="P78">
-        <v>30.391002272</v>
+        <v>30.262989144</v>
       </c>
       <c r="Q78">
-        <v>42.591002272</v>
+        <v>42.462989144</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2943698418544475</v>
+        <v>0.304080493825046</v>
       </c>
       <c r="T78">
-        <v>1.405556471963642</v>
+        <v>1.460466068487637</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.123754688988657</v>
+        <v>4.070199433287506</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1002025935797606</v>
+        <v>0.09988538511445372</v>
       </c>
       <c r="C79">
-        <v>266.6384801245793</v>
+        <v>265.8331933766121</v>
       </c>
       <c r="D79">
-        <v>418.0274801245793</v>
+        <v>420.4791933766122</v>
       </c>
       <c r="E79">
-        <v>52.78900000000002</v>
+        <v>56.04600000000002</v>
       </c>
       <c r="F79">
-        <v>250.789</v>
+        <v>254.046</v>
       </c>
       <c r="G79">
         <v>99.40000000000001</v>
@@ -7759,28 +7759,28 @@
         <v>59</v>
       </c>
       <c r="M79">
-        <v>14.4956042</v>
+        <v>14.6838588</v>
       </c>
       <c r="N79">
-        <v>44.5043958</v>
+        <v>44.3161412</v>
       </c>
       <c r="O79">
-        <v>14.241406656</v>
+        <v>14.181165184</v>
       </c>
       <c r="P79">
-        <v>30.262989144</v>
+        <v>30.134976016</v>
       </c>
       <c r="Q79">
-        <v>42.462989144</v>
+        <v>42.334976016</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.304080493825046</v>
+        <v>0.3146739323384261</v>
       </c>
       <c r="T79">
-        <v>1.460466068487637</v>
+        <v>1.520367446513814</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.070199433287506</v>
+        <v>4.018017389270999</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09988538511445372</v>
+        <v>0.1014483766491469</v>
       </c>
       <c r="C80">
-        <v>265.8331933766121</v>
+        <v>250.7662276716677</v>
       </c>
       <c r="D80">
-        <v>420.4791933766122</v>
+        <v>408.6692276716677</v>
       </c>
       <c r="E80">
-        <v>56.04600000000002</v>
+        <v>59.30300000000003</v>
       </c>
       <c r="F80">
-        <v>254.046</v>
+        <v>257.3030000000001</v>
       </c>
       <c r="G80">
         <v>99.40000000000001</v>
@@ -7841,45 +7841,45 @@
         <v>59</v>
       </c>
       <c r="M80">
-        <v>14.6838588</v>
+        <v>15.7726739</v>
       </c>
       <c r="N80">
-        <v>44.3161412</v>
+        <v>43.2273261</v>
       </c>
       <c r="O80">
-        <v>14.181165184</v>
+        <v>13.832744352</v>
       </c>
       <c r="P80">
-        <v>30.134976016</v>
+        <v>29.394581748</v>
       </c>
       <c r="Q80">
-        <v>42.334976016</v>
+        <v>41.594581748</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3146739323384261</v>
+        <v>0.3262762697578424</v>
       </c>
       <c r="T80">
-        <v>1.520367446513814</v>
+        <v>1.585973717685341</v>
       </c>
       <c r="U80">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V80">
         <v>0.32</v>
       </c>
       <c r="W80">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.018017389270999</v>
+        <v>3.74064666359456</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1014483766491469</v>
+        <v>0.10115496818384</v>
       </c>
       <c r="C81">
-        <v>250.7662276716677</v>
+        <v>249.6753749000619</v>
       </c>
       <c r="D81">
-        <v>408.6692276716677</v>
+        <v>410.835374900062</v>
       </c>
       <c r="E81">
-        <v>59.30300000000003</v>
+        <v>62.56000000000003</v>
       </c>
       <c r="F81">
-        <v>257.3030000000001</v>
+        <v>260.5600000000001</v>
       </c>
       <c r="G81">
         <v>99.40000000000001</v>
@@ -7923,28 +7923,28 @@
         <v>59</v>
       </c>
       <c r="M81">
-        <v>15.7726739</v>
+        <v>15.972328</v>
       </c>
       <c r="N81">
-        <v>43.2273261</v>
+        <v>43.027672</v>
       </c>
       <c r="O81">
-        <v>13.832744352</v>
+        <v>13.76885504</v>
       </c>
       <c r="P81">
-        <v>29.394581748</v>
+        <v>29.25881696</v>
       </c>
       <c r="Q81">
-        <v>41.594581748</v>
+        <v>41.45881695999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3262762697578424</v>
+        <v>0.3390388409192003</v>
       </c>
       <c r="T81">
-        <v>1.585973717685341</v>
+        <v>1.658140615974021</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.74064666359456</v>
+        <v>3.693888580299627</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.10115496818384</v>
+        <v>0.1008615597185332</v>
       </c>
       <c r="C82">
-        <v>249.6753749000619</v>
+        <v>248.6076077779422</v>
       </c>
       <c r="D82">
-        <v>410.835374900062</v>
+        <v>413.0246077779422</v>
       </c>
       <c r="E82">
-        <v>62.56000000000003</v>
+        <v>65.81700000000004</v>
       </c>
       <c r="F82">
-        <v>260.5600000000001</v>
+        <v>263.8170000000001</v>
       </c>
       <c r="G82">
         <v>99.40000000000001</v>
@@ -8005,28 +8005,28 @@
         <v>59</v>
       </c>
       <c r="M82">
-        <v>15.972328</v>
+        <v>16.1719821</v>
       </c>
       <c r="N82">
-        <v>43.027672</v>
+        <v>42.82801789999999</v>
       </c>
       <c r="O82">
-        <v>13.76885504</v>
+        <v>13.704965728</v>
       </c>
       <c r="P82">
-        <v>29.25881696</v>
+        <v>29.12305217199999</v>
       </c>
       <c r="Q82">
-        <v>41.45881695999999</v>
+        <v>41.32305217199999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3390388409192003</v>
+        <v>0.3531448406238591</v>
       </c>
       <c r="T82">
-        <v>1.658140615974021</v>
+        <v>1.737904029872036</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.693888580299627</v>
+        <v>3.648285017579878</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1008615597185332</v>
+        <v>0.1005681512532264</v>
       </c>
       <c r="C83">
-        <v>248.6076077779422</v>
+        <v>247.5632973343556</v>
       </c>
       <c r="D83">
-        <v>413.0246077779422</v>
+        <v>415.2372973343557</v>
       </c>
       <c r="E83">
-        <v>65.81700000000004</v>
+        <v>69.07400000000004</v>
       </c>
       <c r="F83">
-        <v>263.8170000000001</v>
+        <v>267.0740000000001</v>
       </c>
       <c r="G83">
         <v>99.40000000000001</v>
@@ -8087,28 +8087,28 @@
         <v>59</v>
       </c>
       <c r="M83">
-        <v>16.1719821</v>
+        <v>16.3716362</v>
       </c>
       <c r="N83">
-        <v>42.82801789999999</v>
+        <v>42.6283638</v>
       </c>
       <c r="O83">
-        <v>13.704965728</v>
+        <v>13.641076416</v>
       </c>
       <c r="P83">
-        <v>29.12305217199999</v>
+        <v>28.987287384</v>
       </c>
       <c r="Q83">
-        <v>41.32305217199999</v>
+        <v>41.187287384</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3531448406238591</v>
+        <v>0.3688181736290355</v>
       </c>
       <c r="T83">
-        <v>1.737904029872036</v>
+        <v>1.826530045314275</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.648285017579878</v>
+        <v>3.603793736877685</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1005681512532264</v>
+        <v>0.1002747427879195</v>
       </c>
       <c r="C84">
-        <v>247.5632973343556</v>
+        <v>246.5428225920031</v>
       </c>
       <c r="D84">
-        <v>415.2372973343557</v>
+        <v>417.4738225920032</v>
       </c>
       <c r="E84">
-        <v>69.07400000000004</v>
+        <v>72.33100000000005</v>
       </c>
       <c r="F84">
-        <v>267.0740000000001</v>
+        <v>270.3310000000001</v>
       </c>
       <c r="G84">
         <v>99.40000000000001</v>
@@ -8169,28 +8169,28 @@
         <v>59</v>
       </c>
       <c r="M84">
-        <v>16.3716362</v>
+        <v>16.5712903</v>
       </c>
       <c r="N84">
-        <v>42.6283638</v>
+        <v>42.4287097</v>
       </c>
       <c r="O84">
-        <v>13.641076416</v>
+        <v>13.577187104</v>
       </c>
       <c r="P84">
-        <v>28.987287384</v>
+        <v>28.851522596</v>
       </c>
       <c r="Q84">
-        <v>41.187287384</v>
+        <v>41.051522596</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3688181736290355</v>
+        <v>0.3863354281642327</v>
       </c>
       <c r="T84">
-        <v>1.826530045314275</v>
+        <v>1.925582650808541</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.603793736877685</v>
+        <v>3.560374535228557</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1002747427879195</v>
+        <v>0.09998133432261269</v>
       </c>
       <c r="C85">
-        <v>246.5428225920031</v>
+        <v>245.5465707836803</v>
       </c>
       <c r="D85">
-        <v>417.4738225920032</v>
+        <v>419.7345707836803</v>
       </c>
       <c r="E85">
-        <v>72.33100000000005</v>
+        <v>75.58800000000005</v>
       </c>
       <c r="F85">
-        <v>270.3310000000001</v>
+        <v>273.5880000000001</v>
       </c>
       <c r="G85">
         <v>99.40000000000001</v>
@@ -8251,28 +8251,28 @@
         <v>59</v>
       </c>
       <c r="M85">
-        <v>16.5712903</v>
+        <v>16.7709444</v>
       </c>
       <c r="N85">
-        <v>42.4287097</v>
+        <v>42.2290556</v>
       </c>
       <c r="O85">
-        <v>13.577187104</v>
+        <v>13.513297792</v>
       </c>
       <c r="P85">
-        <v>28.851522596</v>
+        <v>28.715757808</v>
       </c>
       <c r="Q85">
-        <v>41.051522596</v>
+        <v>40.915757808</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3863354281642327</v>
+        <v>0.4060423395163295</v>
       </c>
       <c r="T85">
-        <v>1.925582650808541</v>
+        <v>2.037016831989591</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.560374535228557</v>
+        <v>3.517989124094883</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09998133432261269</v>
+        <v>0.1013063258573059</v>
       </c>
       <c r="C86">
-        <v>245.5465707836804</v>
+        <v>232.2700866164852</v>
       </c>
       <c r="D86">
-        <v>419.7345707836803</v>
+        <v>409.7150866164852</v>
       </c>
       <c r="E86">
-        <v>75.58799999999999</v>
+        <v>78.845</v>
       </c>
       <c r="F86">
-        <v>273.588</v>
+        <v>276.845</v>
       </c>
       <c r="G86">
         <v>99.40000000000001</v>
@@ -8333,45 +8333,45 @@
         <v>59</v>
       </c>
       <c r="M86">
-        <v>16.7709444</v>
+        <v>17.7457645</v>
       </c>
       <c r="N86">
-        <v>42.2290556</v>
+        <v>41.25423549999999</v>
       </c>
       <c r="O86">
-        <v>13.513297792</v>
+        <v>13.20135536</v>
       </c>
       <c r="P86">
-        <v>28.715757808</v>
+        <v>28.05288014</v>
       </c>
       <c r="Q86">
-        <v>40.915757808</v>
+        <v>40.25288013999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4060423395163292</v>
+        <v>0.4283768390487057</v>
       </c>
       <c r="T86">
-        <v>2.03701683198959</v>
+        <v>2.16330890399478</v>
       </c>
       <c r="U86">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V86">
         <v>0.32</v>
       </c>
       <c r="W86">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y86">
-        <v>3.517989124094884</v>
+        <v>3.324737009780558</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1013063258573059</v>
+        <v>0.101031957391999</v>
       </c>
       <c r="C87">
-        <v>232.2700866164852</v>
+        <v>231.0483738819752</v>
       </c>
       <c r="D87">
-        <v>409.7150866164852</v>
+        <v>411.7503738819753</v>
       </c>
       <c r="E87">
-        <v>78.845</v>
+        <v>82.102</v>
       </c>
       <c r="F87">
-        <v>276.845</v>
+        <v>280.102</v>
       </c>
       <c r="G87">
         <v>99.40000000000001</v>
@@ -8415,28 +8415,28 @@
         <v>59</v>
       </c>
       <c r="M87">
-        <v>17.7457645</v>
+        <v>17.9545382</v>
       </c>
       <c r="N87">
-        <v>41.25423549999999</v>
+        <v>41.0454618</v>
       </c>
       <c r="O87">
-        <v>13.20135536</v>
+        <v>13.134547776</v>
       </c>
       <c r="P87">
-        <v>28.05288014</v>
+        <v>27.910914024</v>
       </c>
       <c r="Q87">
-        <v>40.25288013999999</v>
+        <v>40.110914024</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4283768390487057</v>
+        <v>0.4539019813714215</v>
       </c>
       <c r="T87">
-        <v>2.16330890399478</v>
+        <v>2.307642700572139</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.324737009780558</v>
+        <v>3.286077277108692</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.101031957391999</v>
+        <v>0.1007575889266922</v>
       </c>
       <c r="C88">
-        <v>231.0483738819752</v>
+        <v>229.8469829503099</v>
       </c>
       <c r="D88">
-        <v>411.7503738819753</v>
+        <v>413.80598295031</v>
       </c>
       <c r="E88">
-        <v>82.102</v>
+        <v>85.35900000000001</v>
       </c>
       <c r="F88">
-        <v>280.102</v>
+        <v>283.359</v>
       </c>
       <c r="G88">
         <v>99.40000000000001</v>
@@ -8497,28 +8497,28 @@
         <v>59</v>
       </c>
       <c r="M88">
-        <v>17.9545382</v>
+        <v>18.1633119</v>
       </c>
       <c r="N88">
-        <v>41.0454618</v>
+        <v>40.8366881</v>
       </c>
       <c r="O88">
-        <v>13.134547776</v>
+        <v>13.067740192</v>
       </c>
       <c r="P88">
-        <v>27.910914024</v>
+        <v>27.768947908</v>
       </c>
       <c r="Q88">
-        <v>40.110914024</v>
+        <v>39.968947908</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4539019813714215</v>
+        <v>0.4833540686668629</v>
       </c>
       <c r="T88">
-        <v>2.307642700572139</v>
+        <v>2.47418169662294</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.286077277108692</v>
+        <v>3.248306273923534</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1007575889266922</v>
+        <v>0.1004832204613853</v>
       </c>
       <c r="C89">
-        <v>229.8469829503099</v>
+        <v>228.6662197103055</v>
       </c>
       <c r="D89">
-        <v>413.80598295031</v>
+        <v>415.8822197103055</v>
       </c>
       <c r="E89">
-        <v>85.35900000000001</v>
+        <v>88.61600000000001</v>
       </c>
       <c r="F89">
-        <v>283.359</v>
+        <v>286.616</v>
       </c>
       <c r="G89">
         <v>99.40000000000001</v>
@@ -8579,28 +8579,28 @@
         <v>59</v>
       </c>
       <c r="M89">
-        <v>18.1633119</v>
+        <v>18.37208560000001</v>
       </c>
       <c r="N89">
-        <v>40.8366881</v>
+        <v>40.62791439999999</v>
       </c>
       <c r="O89">
-        <v>13.067740192</v>
+        <v>13.000932608</v>
       </c>
       <c r="P89">
-        <v>27.768947908</v>
+        <v>27.626981792</v>
       </c>
       <c r="Q89">
-        <v>39.968947908</v>
+        <v>39.826981792</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4833540686668629</v>
+        <v>0.5177148371782111</v>
       </c>
       <c r="T89">
-        <v>2.47418169662294</v>
+        <v>2.668477192015539</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.248306273923534</v>
+        <v>3.211393702628948</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1004832204613853</v>
+        <v>0.1002088519960785</v>
       </c>
       <c r="C90">
-        <v>228.6662197103055</v>
+        <v>227.5063962208216</v>
       </c>
       <c r="D90">
-        <v>415.8822197103055</v>
+        <v>417.9793962208216</v>
       </c>
       <c r="E90">
-        <v>88.61600000000001</v>
+        <v>91.87300000000002</v>
       </c>
       <c r="F90">
-        <v>286.616</v>
+        <v>289.873</v>
       </c>
       <c r="G90">
         <v>99.40000000000001</v>
@@ -8661,28 +8661,28 @@
         <v>59</v>
       </c>
       <c r="M90">
-        <v>18.37208560000001</v>
+        <v>18.5808593</v>
       </c>
       <c r="N90">
-        <v>40.62791439999999</v>
+        <v>40.4191407</v>
       </c>
       <c r="O90">
-        <v>13.000932608</v>
+        <v>12.934125024</v>
       </c>
       <c r="P90">
-        <v>27.626981792</v>
+        <v>27.485015676</v>
       </c>
       <c r="Q90">
-        <v>39.826981792</v>
+        <v>39.685015676</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5177148371782111</v>
+        <v>0.5583230181461681</v>
       </c>
       <c r="T90">
-        <v>2.668477192015539</v>
+        <v>2.898099141115885</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.211393702628948</v>
+        <v>3.175310627318511</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1002088519960785</v>
+        <v>0.09993448353077165</v>
       </c>
       <c r="C91">
-        <v>227.5063962208216</v>
+        <v>226.3678308671185</v>
       </c>
       <c r="D91">
-        <v>417.9793962208216</v>
+        <v>420.0978308671185</v>
       </c>
       <c r="E91">
-        <v>91.87300000000002</v>
+        <v>95.13000000000002</v>
       </c>
       <c r="F91">
-        <v>289.873</v>
+        <v>293.1300000000001</v>
       </c>
       <c r="G91">
         <v>99.40000000000001</v>
@@ -8743,28 +8743,28 @@
         <v>59</v>
       </c>
       <c r="M91">
-        <v>18.5808593</v>
+        <v>18.78963300000001</v>
       </c>
       <c r="N91">
-        <v>40.4191407</v>
+        <v>40.21036699999999</v>
       </c>
       <c r="O91">
-        <v>12.934125024</v>
+        <v>12.86731744</v>
       </c>
       <c r="P91">
-        <v>27.485015676</v>
+        <v>27.34304955999999</v>
       </c>
       <c r="Q91">
-        <v>39.685015676</v>
+        <v>39.54304955999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5583230181461681</v>
+        <v>0.6070528353077166</v>
       </c>
       <c r="T91">
-        <v>2.898099141115885</v>
+        <v>3.173645480036299</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.175310627318511</v>
+        <v>3.140029398126083</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09993448353077165</v>
+        <v>0.09966011506546481</v>
       </c>
       <c r="C92">
-        <v>226.3678308671185</v>
+        <v>225.2508485219945</v>
       </c>
       <c r="D92">
-        <v>420.0978308671185</v>
+        <v>422.2378485219945</v>
       </c>
       <c r="E92">
-        <v>95.13000000000002</v>
+        <v>98.38700000000003</v>
       </c>
       <c r="F92">
-        <v>293.1300000000001</v>
+        <v>296.3870000000001</v>
       </c>
       <c r="G92">
         <v>99.40000000000001</v>
@@ -8825,28 +8825,28 @@
         <v>59</v>
       </c>
       <c r="M92">
-        <v>18.78963300000001</v>
+        <v>18.9984067</v>
       </c>
       <c r="N92">
-        <v>40.21036699999999</v>
+        <v>40.0015933</v>
       </c>
       <c r="O92">
-        <v>12.86731744</v>
+        <v>12.800509856</v>
       </c>
       <c r="P92">
-        <v>27.34304955999999</v>
+        <v>27.201083444</v>
       </c>
       <c r="Q92">
-        <v>39.54304955999999</v>
+        <v>39.40108344399999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6070528353077166</v>
+        <v>0.666611500727387</v>
       </c>
       <c r="T92">
-        <v>3.173645480036299</v>
+        <v>3.510424338716805</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.140029398126083</v>
+        <v>3.105523580564258</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09966011506546481</v>
+        <v>0.09938574660015798</v>
       </c>
       <c r="C93">
-        <v>225.2508485219945</v>
+        <v>224.1557807118708</v>
       </c>
       <c r="D93">
-        <v>422.2378485219945</v>
+        <v>424.3997807118708</v>
       </c>
       <c r="E93">
-        <v>98.38700000000003</v>
+        <v>101.644</v>
       </c>
       <c r="F93">
-        <v>296.3870000000001</v>
+        <v>299.6440000000001</v>
       </c>
       <c r="G93">
         <v>99.40000000000001</v>
@@ -8907,28 +8907,28 @@
         <v>59</v>
       </c>
       <c r="M93">
-        <v>18.9984067</v>
+        <v>19.20718040000001</v>
       </c>
       <c r="N93">
-        <v>40.0015933</v>
+        <v>39.79281959999999</v>
       </c>
       <c r="O93">
-        <v>12.800509856</v>
+        <v>12.733702272</v>
       </c>
       <c r="P93">
-        <v>27.201083444</v>
+        <v>27.059117328</v>
       </c>
       <c r="Q93">
-        <v>39.40108344399999</v>
+        <v>39.25911732799999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.666611500727387</v>
+        <v>0.741059832501975</v>
       </c>
       <c r="T93">
-        <v>3.510424338716805</v>
+        <v>3.931397912067439</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.105523580564258</v>
+        <v>3.071767889471168</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09938574660015798</v>
+        <v>0.09911137813485113</v>
       </c>
       <c r="C94">
-        <v>224.1557807118708</v>
+        <v>223.0829657880086</v>
       </c>
       <c r="D94">
-        <v>424.3997807118708</v>
+        <v>426.5839657880086</v>
       </c>
       <c r="E94">
-        <v>101.644</v>
+        <v>104.901</v>
       </c>
       <c r="F94">
-        <v>299.6440000000001</v>
+        <v>302.9010000000001</v>
       </c>
       <c r="G94">
         <v>99.40000000000001</v>
@@ -8989,28 +8989,28 @@
         <v>59</v>
       </c>
       <c r="M94">
-        <v>19.20718040000001</v>
+        <v>19.4159541</v>
       </c>
       <c r="N94">
-        <v>39.79281959999999</v>
+        <v>39.58404589999999</v>
       </c>
       <c r="O94">
-        <v>12.733702272</v>
+        <v>12.666894688</v>
       </c>
       <c r="P94">
-        <v>27.059117328</v>
+        <v>26.91715121199999</v>
       </c>
       <c r="Q94">
-        <v>39.25911732799999</v>
+        <v>39.117151212</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.741059832501975</v>
+        <v>0.8367791162121596</v>
       </c>
       <c r="T94">
-        <v>3.931397912067439</v>
+        <v>4.472649649232538</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.071767889471168</v>
+        <v>3.03873812721879</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09911137813485113</v>
+        <v>0.09883700966954428</v>
       </c>
       <c r="C95">
-        <v>223.0829657880086</v>
+        <v>222.0327491030371</v>
       </c>
       <c r="D95">
-        <v>426.5839657880086</v>
+        <v>428.7907491030372</v>
       </c>
       <c r="E95">
-        <v>104.901</v>
+        <v>108.158</v>
       </c>
       <c r="F95">
-        <v>302.9010000000001</v>
+        <v>306.1580000000001</v>
       </c>
       <c r="G95">
         <v>99.40000000000001</v>
@@ -9071,28 +9071,28 @@
         <v>59</v>
       </c>
       <c r="M95">
-        <v>19.4159541</v>
+        <v>19.62472780000001</v>
       </c>
       <c r="N95">
-        <v>39.58404589999999</v>
+        <v>39.3752722</v>
       </c>
       <c r="O95">
-        <v>12.666894688</v>
+        <v>12.600087104</v>
       </c>
       <c r="P95">
-        <v>26.91715121199999</v>
+        <v>26.775185096</v>
       </c>
       <c r="Q95">
-        <v>39.117151212</v>
+        <v>38.975185096</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8367791162121596</v>
+        <v>0.9644048278257391</v>
       </c>
       <c r="T95">
-        <v>4.472649649232538</v>
+        <v>5.194318632119339</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.03873812721879</v>
+        <v>3.006411125865398</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09883700966954428</v>
+        <v>0.1036014412042375</v>
       </c>
       <c r="C96">
-        <v>222.0327491030371</v>
+        <v>183.4315755971792</v>
       </c>
       <c r="D96">
-        <v>428.7907491030372</v>
+        <v>393.4465755971792</v>
       </c>
       <c r="E96">
-        <v>108.158</v>
+        <v>111.415</v>
       </c>
       <c r="F96">
-        <v>306.1580000000001</v>
+        <v>309.4150000000001</v>
       </c>
       <c r="G96">
         <v>99.40000000000001</v>
@@ -9153,45 +9153,45 @@
         <v>59</v>
       </c>
       <c r="M96">
-        <v>19.62472780000001</v>
+        <v>22.24693850000001</v>
       </c>
       <c r="N96">
-        <v>39.3752722</v>
+        <v>36.75306149999999</v>
       </c>
       <c r="O96">
-        <v>12.600087104</v>
+        <v>11.76097968</v>
       </c>
       <c r="P96">
-        <v>26.775185096</v>
+        <v>24.99208182</v>
       </c>
       <c r="Q96">
-        <v>38.975185096</v>
+        <v>37.19208182</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9644048278257391</v>
+        <v>1.143080824084751</v>
       </c>
       <c r="T96">
-        <v>5.194318632119339</v>
+        <v>6.204655208160861</v>
       </c>
       <c r="U96">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V96">
         <v>0.32</v>
       </c>
       <c r="W96">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y96">
-        <v>3.006411125865398</v>
+        <v>2.652050303460856</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1036014412042375</v>
+        <v>0.1033801127389306</v>
       </c>
       <c r="C97">
-        <v>183.4315755971792</v>
+        <v>181.6869194015754</v>
       </c>
       <c r="D97">
-        <v>393.4465755971792</v>
+        <v>394.9589194015754</v>
       </c>
       <c r="E97">
-        <v>111.415</v>
+        <v>114.6720000000001</v>
       </c>
       <c r="F97">
-        <v>309.4150000000001</v>
+        <v>312.6720000000001</v>
       </c>
       <c r="G97">
         <v>99.40000000000001</v>
@@ -9235,28 +9235,28 @@
         <v>59</v>
       </c>
       <c r="M97">
-        <v>22.24693850000001</v>
+        <v>22.48111680000001</v>
       </c>
       <c r="N97">
-        <v>36.75306149999999</v>
+        <v>36.51888319999999</v>
       </c>
       <c r="O97">
-        <v>11.76097968</v>
+        <v>11.686042624</v>
       </c>
       <c r="P97">
-        <v>24.99208182</v>
+        <v>24.832840576</v>
       </c>
       <c r="Q97">
-        <v>37.19208182</v>
+        <v>37.032840576</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.143080824084751</v>
+        <v>1.411094818473268</v>
       </c>
       <c r="T97">
-        <v>6.204655208160861</v>
+        <v>7.720160072223144</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.652050303460856</v>
+        <v>2.624424779466471</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1033801127389306</v>
+        <v>0.1031587842736238</v>
       </c>
       <c r="C98">
-        <v>181.6869194015754</v>
+        <v>179.9539344691436</v>
       </c>
       <c r="D98">
-        <v>394.9589194015754</v>
+        <v>396.4829344691436</v>
       </c>
       <c r="E98">
-        <v>114.672</v>
+        <v>117.929</v>
       </c>
       <c r="F98">
-        <v>312.672</v>
+        <v>315.929</v>
       </c>
       <c r="G98">
         <v>99.40000000000001</v>
@@ -9317,28 +9317,28 @@
         <v>59</v>
       </c>
       <c r="M98">
-        <v>22.4811168</v>
+        <v>22.7152951</v>
       </c>
       <c r="N98">
-        <v>36.5188832</v>
+        <v>36.28470489999999</v>
       </c>
       <c r="O98">
-        <v>11.686042624</v>
+        <v>11.611105568</v>
       </c>
       <c r="P98">
-        <v>24.832840576</v>
+        <v>24.67359933199999</v>
       </c>
       <c r="Q98">
-        <v>37.032840576</v>
+        <v>36.873599332</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.411094818473264</v>
+        <v>1.857784809120791</v>
       </c>
       <c r="T98">
-        <v>7.720160072223123</v>
+        <v>10.24600151232692</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.624424779466472</v>
+        <v>2.597368853904961</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1031587842736238</v>
+        <v>0.1029374558083169</v>
       </c>
       <c r="C99">
-        <v>179.9539344691436</v>
+        <v>178.2327564297993</v>
       </c>
       <c r="D99">
-        <v>396.4829344691436</v>
+        <v>398.0187564297994</v>
       </c>
       <c r="E99">
-        <v>117.929</v>
+        <v>121.186</v>
       </c>
       <c r="F99">
-        <v>315.929</v>
+        <v>319.186</v>
       </c>
       <c r="G99">
         <v>99.40000000000001</v>
@@ -9399,28 +9399,28 @@
         <v>59</v>
       </c>
       <c r="M99">
-        <v>22.7152951</v>
+        <v>22.94947340000001</v>
       </c>
       <c r="N99">
-        <v>36.28470489999999</v>
+        <v>36.0505266</v>
       </c>
       <c r="O99">
-        <v>11.611105568</v>
+        <v>11.536168512</v>
       </c>
       <c r="P99">
-        <v>24.67359933199999</v>
+        <v>24.514358088</v>
       </c>
       <c r="Q99">
-        <v>36.873599332</v>
+        <v>36.714358088</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.857784809120791</v>
+        <v>2.751164790415844</v>
       </c>
       <c r="T99">
-        <v>10.24600151232692</v>
+        <v>15.2976843925345</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.597368853904961</v>
+        <v>2.570865090089605</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1029374558083169</v>
+        <v>0.1027161273430101</v>
       </c>
       <c r="C100">
-        <v>178.2327564297993</v>
+        <v>176.523523023142</v>
       </c>
       <c r="D100">
-        <v>398.0187564297994</v>
+        <v>399.566523023142</v>
       </c>
       <c r="E100">
-        <v>121.186</v>
+        <v>124.443</v>
       </c>
       <c r="F100">
-        <v>319.186</v>
+        <v>322.443</v>
       </c>
       <c r="G100">
         <v>99.40000000000001</v>
@@ -9481,28 +9481,28 @@
         <v>59</v>
       </c>
       <c r="M100">
-        <v>22.94947340000001</v>
+        <v>23.18365170000001</v>
       </c>
       <c r="N100">
-        <v>36.0505266</v>
+        <v>35.81634829999999</v>
       </c>
       <c r="O100">
-        <v>11.536168512</v>
+        <v>11.461231456</v>
       </c>
       <c r="P100">
-        <v>24.514358088</v>
+        <v>24.35511684399999</v>
       </c>
       <c r="Q100">
-        <v>36.714358088</v>
+        <v>36.555116844</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.751164790415844</v>
+        <v>5.431304734301006</v>
       </c>
       <c r="T100">
-        <v>15.2976843925345</v>
+        <v>30.45273303315726</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.570865090089605</v>
+        <v>2.544896755846275</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1027161273430101</v>
-      </c>
-      <c r="C101">
-        <v>176.523523023142</v>
-      </c>
-      <c r="D101">
-        <v>399.566523023142</v>
-      </c>
-      <c r="E101">
-        <v>124.443</v>
-      </c>
-      <c r="F101">
-        <v>322.443</v>
-      </c>
-      <c r="G101">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="H101">
-        <v>127.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>71.2</v>
-      </c>
-      <c r="K101">
-        <v>12.2</v>
-      </c>
-      <c r="L101">
-        <v>59</v>
-      </c>
-      <c r="M101">
-        <v>23.18365170000001</v>
-      </c>
-      <c r="N101">
-        <v>35.81634829999999</v>
-      </c>
-      <c r="O101">
-        <v>11.461231456</v>
-      </c>
-      <c r="P101">
-        <v>24.35511684399999</v>
-      </c>
-      <c r="Q101">
-        <v>36.555116844</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.431304734301006</v>
-      </c>
-      <c r="T101">
-        <v>30.45273303315726</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.32</v>
-      </c>
-      <c r="W101">
-        <v>0.048892</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.544896755846275</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
